--- a/static/TALENKAART_DATA/talenkaart_data.xlsx
+++ b/static/TALENKAART_DATA/talenkaart_data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1244">
   <si>
     <t>Locatie</t>
   </si>
@@ -521,7 +521,7 @@
     <t>eng,fra,spa</t>
   </si>
   <si>
-    <t>nld,ara ("Marokkaans")</t>
+    <t>nld,ary</t>
   </si>
   <si>
     <t>fra,dui,eng</t>
@@ -545,7 +545,7 @@
     <t>nld,eng,spa,fra</t>
   </si>
   <si>
-    <t>ara (Marokkaans)</t>
+    <t>ary</t>
   </si>
   <si>
     <t>nld,eng,"nigeriaans"</t>
@@ -557,7 +557,7 @@
     <t>"chinees",tur</t>
   </si>
   <si>
-    <t>"chinees","indiaas", "afrikaans"</t>
+    <t>"chinees","indiaas", afr</t>
   </si>
   <si>
     <t>nld,eng,pap,srn</t>
@@ -1382,6 +1382,9 @@
     <t>Barlaeus Gymnasium</t>
   </si>
   <si>
+    <t>Centrum</t>
+  </si>
+  <si>
     <t>nld,ita,eng,spa,fra</t>
   </si>
   <si>
@@ -1883,9 +1886,6 @@
     <t>Jordaan College</t>
   </si>
   <si>
-    <t>Centrum</t>
-  </si>
-  <si>
     <t>nld,cat,spa,eng</t>
   </si>
   <si>
@@ -1898,7 +1898,7 @@
     <t>Praktijkcollege De Atlant</t>
   </si>
   <si>
-    <t>Kolom praktijkcollege Noord</t>
+    <t>Kolom Praktijkcollege Noord</t>
   </si>
   <si>
     <t>Koninklijke Visio Onderwijs</t>
@@ -2456,9 +2456,6 @@
     <t>52.40393390117781, 4.90912170838217</t>
   </si>
   <si>
-    <t>Praktijkcollege Noord</t>
-  </si>
-  <si>
     <t>52.4206890794613, 4.878765166054527</t>
   </si>
   <si>
@@ -2831,6 +2828,9 @@
     <t>52.31903955113328, 4.965709650359623</t>
   </si>
   <si>
+    <t>52.36229237389858, 4.884754723468775</t>
+  </si>
+  <si>
     <t>ISO 639-3</t>
   </si>
   <si>
@@ -3282,12 +3282,6 @@
   </si>
   <si>
     <t>Dumun</t>
-  </si>
-  <si>
-    <t>tw</t>
-  </si>
-  <si>
-    <t>ary</t>
   </si>
   <si>
     <t>Marokkaans-Arabisch</t>
@@ -12255,45 +12249,47 @@
       <c r="A475" t="s" s="3">
         <v>446</v>
       </c>
-      <c r="B475" s="3"/>
+      <c r="B475" t="s" s="3">
+        <v>447</v>
+      </c>
       <c r="C475" s="3"/>
       <c r="D475" t="s" s="3">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E475" s="4"/>
       <c r="F475" s="4"/>
     </row>
     <row r="476" ht="13.65" customHeight="1">
       <c r="A476" t="s" s="3">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B476" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C476" s="3"/>
       <c r="D476" t="s" s="3">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E476" s="4"/>
       <c r="F476" s="4"/>
     </row>
     <row r="477" ht="13.65" customHeight="1">
       <c r="A477" t="s" s="3">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B477" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C477" s="3"/>
       <c r="D477" t="s" s="3">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E477" s="4"/>
       <c r="F477" s="4"/>
     </row>
     <row r="478" ht="13.65" customHeight="1">
       <c r="A478" t="s" s="3">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B478" t="s" s="3">
         <v>178</v>
@@ -12307,63 +12303,63 @@
     </row>
     <row r="479" ht="13.65" customHeight="1">
       <c r="A479" t="s" s="3">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B479" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C479" s="3"/>
       <c r="D479" t="s" s="3">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E479" s="4"/>
       <c r="F479" s="4"/>
     </row>
     <row r="480" ht="13.65" customHeight="1">
       <c r="A480" t="s" s="3">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B480" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C480" s="3"/>
       <c r="D480" t="s" s="3">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E480" s="4"/>
       <c r="F480" s="4"/>
     </row>
     <row r="481" ht="13.65" customHeight="1">
       <c r="A481" t="s" s="3">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B481" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C481" s="3"/>
       <c r="D481" t="s" s="3">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E481" s="4"/>
       <c r="F481" s="4"/>
     </row>
     <row r="482" ht="13.65" customHeight="1">
       <c r="A482" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B482" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C482" s="3"/>
       <c r="D482" t="s" s="3">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E482" s="4"/>
       <c r="F482" s="4"/>
     </row>
     <row r="483" ht="13.65" customHeight="1">
       <c r="A483" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B483" t="s" s="3">
         <v>347</v>
@@ -12377,91 +12373,91 @@
     </row>
     <row r="484" ht="13.65" customHeight="1">
       <c r="A484" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B484" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C484" s="3"/>
       <c r="D484" t="s" s="3">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E484" s="4"/>
       <c r="F484" s="4"/>
     </row>
     <row r="485" ht="13.65" customHeight="1">
       <c r="A485" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B485" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C485" s="3"/>
       <c r="D485" t="s" s="3">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E485" s="4"/>
       <c r="F485" s="4"/>
     </row>
     <row r="486" ht="13.65" customHeight="1">
       <c r="A486" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B486" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C486" s="3"/>
       <c r="D486" t="s" s="3">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E486" s="4"/>
       <c r="F486" s="4"/>
     </row>
     <row r="487" ht="13.65" customHeight="1">
       <c r="A487" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B487" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C487" s="3"/>
       <c r="D487" t="s" s="3">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E487" s="4"/>
       <c r="F487" s="4"/>
     </row>
     <row r="488" ht="13.65" customHeight="1">
       <c r="A488" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B488" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C488" s="3"/>
       <c r="D488" t="s" s="3">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E488" s="4"/>
       <c r="F488" s="4"/>
     </row>
     <row r="489" ht="13.65" customHeight="1">
       <c r="A489" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B489" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C489" s="3"/>
       <c r="D489" t="s" s="3">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E489" s="4"/>
       <c r="F489" s="4"/>
     </row>
     <row r="490" ht="13.65" customHeight="1">
       <c r="A490" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B490" t="s" s="3">
         <v>347</v>
@@ -12475,7 +12471,7 @@
     </row>
     <row r="491" ht="13.65" customHeight="1">
       <c r="A491" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B491" t="s" s="3">
         <v>347</v>
@@ -12489,21 +12485,21 @@
     </row>
     <row r="492" ht="13.65" customHeight="1">
       <c r="A492" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B492" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C492" s="3"/>
       <c r="D492" t="s" s="3">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E492" s="4"/>
       <c r="F492" s="4"/>
     </row>
     <row r="493" ht="13.65" customHeight="1">
       <c r="A493" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B493" t="s" s="3">
         <v>347</v>
@@ -12517,49 +12513,49 @@
     </row>
     <row r="494" ht="13.65" customHeight="1">
       <c r="A494" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B494" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C494" s="3"/>
       <c r="D494" t="s" s="3">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E494" s="4"/>
       <c r="F494" s="4"/>
     </row>
     <row r="495" ht="13.65" customHeight="1">
       <c r="A495" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B495" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C495" s="3"/>
       <c r="D495" t="s" s="3">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E495" s="4"/>
       <c r="F495" s="4"/>
     </row>
     <row r="496" ht="13.65" customHeight="1">
       <c r="A496" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B496" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C496" s="3"/>
       <c r="D496" t="s" s="3">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E496" s="4"/>
       <c r="F496" s="4"/>
     </row>
     <row r="497" ht="13.65" customHeight="1">
       <c r="A497" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B497" t="s" s="3">
         <v>347</v>
@@ -12573,7 +12569,7 @@
     </row>
     <row r="498" ht="13.65" customHeight="1">
       <c r="A498" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B498" t="s" s="3">
         <v>347</v>
@@ -12587,21 +12583,21 @@
     </row>
     <row r="499" ht="13.65" customHeight="1">
       <c r="A499" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B499" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C499" s="3"/>
       <c r="D499" t="s" s="3">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E499" s="4"/>
       <c r="F499" s="4"/>
     </row>
     <row r="500" ht="13.65" customHeight="1">
       <c r="A500" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B500" t="s" s="3">
         <v>347</v>
@@ -12615,21 +12611,21 @@
     </row>
     <row r="501" ht="13.65" customHeight="1">
       <c r="A501" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B501" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C501" s="3"/>
       <c r="D501" t="s" s="3">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E501" s="4"/>
       <c r="F501" s="4"/>
     </row>
     <row r="502" ht="13.65" customHeight="1">
       <c r="A502" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B502" t="s" s="3">
         <v>347</v>
@@ -12643,21 +12639,21 @@
     </row>
     <row r="503" ht="13.65" customHeight="1">
       <c r="A503" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B503" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C503" s="3"/>
       <c r="D503" t="s" s="3">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E503" s="4"/>
       <c r="F503" s="4"/>
     </row>
     <row r="504" ht="13.65" customHeight="1">
       <c r="A504" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B504" t="s" s="3">
         <v>347</v>
@@ -12671,7 +12667,7 @@
     </row>
     <row r="505" ht="13.65" customHeight="1">
       <c r="A505" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B505" t="s" s="3">
         <v>347</v>
@@ -12685,35 +12681,35 @@
     </row>
     <row r="506" ht="13.65" customHeight="1">
       <c r="A506" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B506" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C506" s="3"/>
       <c r="D506" t="s" s="3">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E506" s="4"/>
       <c r="F506" s="4"/>
     </row>
     <row r="507" ht="13.65" customHeight="1">
       <c r="A507" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B507" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C507" s="3"/>
       <c r="D507" t="s" s="3">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E507" s="4"/>
       <c r="F507" s="4"/>
     </row>
     <row r="508" ht="13.65" customHeight="1">
       <c r="A508" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B508" t="s" s="3">
         <v>347</v>
@@ -12727,7 +12723,7 @@
     </row>
     <row r="509" ht="13.65" customHeight="1">
       <c r="A509" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B509" t="s" s="3">
         <v>347</v>
@@ -12741,7 +12737,7 @@
     </row>
     <row r="510" ht="13.65" customHeight="1">
       <c r="A510" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B510" t="s" s="3">
         <v>347</v>
@@ -12755,7 +12751,7 @@
     </row>
     <row r="511" ht="13.65" customHeight="1">
       <c r="A511" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B511" t="s" s="3">
         <v>347</v>
@@ -12769,63 +12765,63 @@
     </row>
     <row r="512" ht="13.65" customHeight="1">
       <c r="A512" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B512" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C512" s="3"/>
       <c r="D512" t="s" s="3">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E512" s="4"/>
       <c r="F512" s="4"/>
     </row>
     <row r="513" ht="13.65" customHeight="1">
       <c r="A513" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B513" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C513" s="3"/>
       <c r="D513" t="s" s="3">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E513" s="4"/>
       <c r="F513" s="4"/>
     </row>
     <row r="514" ht="13.65" customHeight="1">
       <c r="A514" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B514" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C514" s="3"/>
       <c r="D514" t="s" s="3">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E514" s="4"/>
       <c r="F514" s="4"/>
     </row>
     <row r="515" ht="13.65" customHeight="1">
       <c r="A515" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B515" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C515" s="3"/>
       <c r="D515" t="s" s="3">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E515" s="4"/>
       <c r="F515" s="4"/>
     </row>
     <row r="516" ht="13.65" customHeight="1">
       <c r="A516" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B516" t="s" s="3">
         <v>347</v>
@@ -12839,49 +12835,49 @@
     </row>
     <row r="517" ht="13.65" customHeight="1">
       <c r="A517" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B517" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C517" s="3"/>
       <c r="D517" t="s" s="3">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E517" s="4"/>
       <c r="F517" s="4"/>
     </row>
     <row r="518" ht="13.65" customHeight="1">
       <c r="A518" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B518" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C518" s="3"/>
       <c r="D518" t="s" s="3">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E518" s="4"/>
       <c r="F518" s="4"/>
     </row>
     <row r="519" ht="13.65" customHeight="1">
       <c r="A519" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B519" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C519" s="3"/>
       <c r="D519" t="s" s="3">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E519" s="4"/>
       <c r="F519" s="4"/>
     </row>
     <row r="520" ht="13.65" customHeight="1">
       <c r="A520" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B520" t="s" s="3">
         <v>347</v>
@@ -12895,21 +12891,21 @@
     </row>
     <row r="521" ht="13.65" customHeight="1">
       <c r="A521" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B521" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C521" s="3"/>
       <c r="D521" t="s" s="3">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E521" s="4"/>
       <c r="F521" s="4"/>
     </row>
     <row r="522" ht="13.65" customHeight="1">
       <c r="A522" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B522" t="s" s="3">
         <v>347</v>
@@ -12923,35 +12919,35 @@
     </row>
     <row r="523" ht="13.65" customHeight="1">
       <c r="A523" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B523" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C523" s="3"/>
       <c r="D523" t="s" s="3">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E523" s="4"/>
       <c r="F523" s="4"/>
     </row>
     <row r="524" ht="13.65" customHeight="1">
       <c r="A524" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B524" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C524" s="3"/>
       <c r="D524" t="s" s="3">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E524" s="4"/>
       <c r="F524" s="4"/>
     </row>
     <row r="525" ht="13.65" customHeight="1">
       <c r="A525" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B525" t="s" s="3">
         <v>347</v>
@@ -12965,21 +12961,21 @@
     </row>
     <row r="526" ht="13.65" customHeight="1">
       <c r="A526" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B526" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C526" s="3"/>
       <c r="D526" t="s" s="3">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E526" s="4"/>
       <c r="F526" s="4"/>
     </row>
     <row r="527" ht="13.65" customHeight="1">
       <c r="A527" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B527" t="s" s="3">
         <v>347</v>
@@ -12993,7 +12989,7 @@
     </row>
     <row r="528" ht="13.65" customHeight="1">
       <c r="A528" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B528" t="s" s="3">
         <v>347</v>
@@ -13007,7 +13003,7 @@
     </row>
     <row r="529" ht="13.65" customHeight="1">
       <c r="A529" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B529" t="s" s="3">
         <v>347</v>
@@ -13021,35 +13017,35 @@
     </row>
     <row r="530" ht="13.65" customHeight="1">
       <c r="A530" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B530" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C530" s="3"/>
       <c r="D530" t="s" s="3">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E530" s="4"/>
       <c r="F530" s="4"/>
     </row>
     <row r="531" ht="13.65" customHeight="1">
       <c r="A531" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B531" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C531" s="3"/>
       <c r="D531" t="s" s="3">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E531" s="4"/>
       <c r="F531" s="4"/>
     </row>
     <row r="532" ht="13.65" customHeight="1">
       <c r="A532" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B532" t="s" s="3">
         <v>347</v>
@@ -13063,21 +13059,21 @@
     </row>
     <row r="533" ht="13.65" customHeight="1">
       <c r="A533" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B533" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C533" s="3"/>
       <c r="D533" t="s" s="3">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E533" s="4"/>
       <c r="F533" s="4"/>
     </row>
     <row r="534" ht="13.65" customHeight="1">
       <c r="A534" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B534" t="s" s="3">
         <v>347</v>
@@ -13091,7 +13087,7 @@
     </row>
     <row r="535" ht="13.65" customHeight="1">
       <c r="A535" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B535" t="s" s="3">
         <v>347</v>
@@ -13105,35 +13101,35 @@
     </row>
     <row r="536" ht="13.65" customHeight="1">
       <c r="A536" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B536" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C536" s="3"/>
       <c r="D536" t="s" s="3">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E536" s="4"/>
       <c r="F536" s="4"/>
     </row>
     <row r="537" ht="13.65" customHeight="1">
       <c r="A537" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B537" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C537" s="3"/>
       <c r="D537" t="s" s="3">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E537" s="4"/>
       <c r="F537" s="4"/>
     </row>
     <row r="538" ht="13.65" customHeight="1">
       <c r="A538" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B538" t="s" s="3">
         <v>347</v>
@@ -13147,7 +13143,7 @@
     </row>
     <row r="539" ht="13.65" customHeight="1">
       <c r="A539" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B539" t="s" s="3">
         <v>347</v>
@@ -13161,35 +13157,35 @@
     </row>
     <row r="540" ht="13.65" customHeight="1">
       <c r="A540" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B540" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C540" s="3"/>
       <c r="D540" t="s" s="3">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E540" s="4"/>
       <c r="F540" s="4"/>
     </row>
     <row r="541" ht="13.65" customHeight="1">
       <c r="A541" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B541" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C541" s="3"/>
       <c r="D541" t="s" s="3">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E541" s="4"/>
       <c r="F541" s="4"/>
     </row>
     <row r="542" ht="13.65" customHeight="1">
       <c r="A542" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B542" t="s" s="3">
         <v>347</v>
@@ -13203,7 +13199,7 @@
     </row>
     <row r="543" ht="13.65" customHeight="1">
       <c r="A543" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B543" t="s" s="3">
         <v>347</v>
@@ -13217,7 +13213,7 @@
     </row>
     <row r="544" ht="13.65" customHeight="1">
       <c r="A544" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B544" t="s" s="3">
         <v>347</v>
@@ -13231,7 +13227,7 @@
     </row>
     <row r="545" ht="13.65" customHeight="1">
       <c r="A545" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B545" t="s" s="3">
         <v>347</v>
@@ -13245,21 +13241,21 @@
     </row>
     <row r="546" ht="13.65" customHeight="1">
       <c r="A546" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B546" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C546" s="3"/>
       <c r="D546" t="s" s="3">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E546" s="4"/>
       <c r="F546" s="4"/>
     </row>
     <row r="547" ht="13.65" customHeight="1">
       <c r="A547" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B547" t="s" s="3">
         <v>347</v>
@@ -13273,7 +13269,7 @@
     </row>
     <row r="548" ht="13.65" customHeight="1">
       <c r="A548" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B548" t="s" s="3">
         <v>347</v>
@@ -13287,7 +13283,7 @@
     </row>
     <row r="549" ht="13.65" customHeight="1">
       <c r="A549" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B549" t="s" s="3">
         <v>347</v>
@@ -13301,175 +13297,175 @@
     </row>
     <row r="550" ht="13.65" customHeight="1">
       <c r="A550" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B550" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C550" s="3"/>
       <c r="D550" t="s" s="3">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E550" s="4"/>
       <c r="F550" s="4"/>
     </row>
     <row r="551" ht="13.65" customHeight="1">
       <c r="A551" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B551" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C551" s="3"/>
       <c r="D551" t="s" s="3">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E551" s="4"/>
       <c r="F551" s="4"/>
     </row>
     <row r="552" ht="13.65" customHeight="1">
       <c r="A552" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B552" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C552" s="3"/>
       <c r="D552" t="s" s="3">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E552" s="4"/>
       <c r="F552" s="4"/>
     </row>
     <row r="553" ht="13.65" customHeight="1">
       <c r="A553" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B553" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C553" s="3"/>
       <c r="D553" t="s" s="3">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E553" s="4"/>
       <c r="F553" s="4"/>
     </row>
     <row r="554" ht="13.65" customHeight="1">
       <c r="A554" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B554" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C554" s="3"/>
       <c r="D554" t="s" s="3">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E554" s="4"/>
       <c r="F554" s="4"/>
     </row>
     <row r="555" ht="13.65" customHeight="1">
       <c r="A555" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B555" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C555" s="3"/>
       <c r="D555" t="s" s="3">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E555" s="4"/>
       <c r="F555" s="4"/>
     </row>
     <row r="556" ht="13.65" customHeight="1">
       <c r="A556" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B556" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C556" s="3"/>
       <c r="D556" t="s" s="3">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E556" s="4"/>
       <c r="F556" s="4"/>
     </row>
     <row r="557" ht="13.65" customHeight="1">
       <c r="A557" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B557" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C557" s="3"/>
       <c r="D557" t="s" s="3">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E557" s="4"/>
       <c r="F557" s="4"/>
     </row>
     <row r="558" ht="13.65" customHeight="1">
       <c r="A558" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B558" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C558" s="3"/>
       <c r="D558" t="s" s="3">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E558" s="4"/>
       <c r="F558" s="4"/>
     </row>
     <row r="559" ht="13.65" customHeight="1">
       <c r="A559" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B559" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C559" s="3"/>
       <c r="D559" t="s" s="3">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E559" s="4"/>
       <c r="F559" s="4"/>
     </row>
     <row r="560" ht="13.65" customHeight="1">
       <c r="A560" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B560" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C560" s="3"/>
       <c r="D560" t="s" s="3">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E560" s="4"/>
       <c r="F560" s="4"/>
     </row>
     <row r="561" ht="13.65" customHeight="1">
       <c r="A561" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B561" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C561" s="3"/>
       <c r="D561" t="s" s="3">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E561" s="4"/>
       <c r="F561" s="4"/>
     </row>
     <row r="562" ht="13.65" customHeight="1">
       <c r="A562" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B562" t="s" s="3">
         <v>347</v>
@@ -13483,7 +13479,7 @@
     </row>
     <row r="563" ht="13.65" customHeight="1">
       <c r="A563" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B563" t="s" s="3">
         <v>347</v>
@@ -13497,119 +13493,119 @@
     </row>
     <row r="564" ht="13.65" customHeight="1">
       <c r="A564" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B564" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C564" s="3"/>
       <c r="D564" t="s" s="3">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E564" s="4"/>
       <c r="F564" s="4"/>
     </row>
     <row r="565" ht="13.65" customHeight="1">
       <c r="A565" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B565" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C565" s="3"/>
       <c r="D565" t="s" s="3">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E565" s="4"/>
       <c r="F565" s="4"/>
     </row>
     <row r="566" ht="13.65" customHeight="1">
       <c r="A566" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B566" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C566" s="3"/>
       <c r="D566" t="s" s="3">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E566" s="4"/>
       <c r="F566" s="4"/>
     </row>
     <row r="567" ht="13.65" customHeight="1">
       <c r="A567" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B567" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C567" s="3"/>
       <c r="D567" t="s" s="3">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E567" s="4"/>
       <c r="F567" s="4"/>
     </row>
     <row r="568" ht="13.65" customHeight="1">
       <c r="A568" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B568" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C568" s="3"/>
       <c r="D568" t="s" s="3">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E568" s="4"/>
       <c r="F568" s="4"/>
     </row>
     <row r="569" ht="13.65" customHeight="1">
       <c r="A569" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B569" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C569" s="3"/>
       <c r="D569" t="s" s="3">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E569" s="4"/>
       <c r="F569" s="4"/>
     </row>
     <row r="570" ht="13.65" customHeight="1">
       <c r="A570" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B570" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C570" s="3"/>
       <c r="D570" t="s" s="3">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E570" s="4"/>
       <c r="F570" s="4"/>
     </row>
     <row r="571" ht="13.65" customHeight="1">
       <c r="A571" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B571" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C571" s="3"/>
       <c r="D571" t="s" s="3">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E571" s="4"/>
       <c r="F571" s="4"/>
     </row>
     <row r="572" ht="13.65" customHeight="1">
       <c r="A572" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B572" t="s" s="3">
         <v>347</v>
@@ -13623,7 +13619,7 @@
     </row>
     <row r="573" ht="13.65" customHeight="1">
       <c r="A573" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B573" t="s" s="3">
         <v>347</v>
@@ -13637,7 +13633,7 @@
     </row>
     <row r="574" ht="13.65" customHeight="1">
       <c r="A574" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B574" t="s" s="3">
         <v>347</v>
@@ -13651,35 +13647,35 @@
     </row>
     <row r="575" ht="13.65" customHeight="1">
       <c r="A575" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B575" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C575" s="3"/>
       <c r="D575" t="s" s="3">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E575" s="4"/>
       <c r="F575" s="4"/>
     </row>
     <row r="576" ht="13.65" customHeight="1">
       <c r="A576" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B576" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C576" s="3"/>
       <c r="D576" t="s" s="3">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E576" s="4"/>
       <c r="F576" s="4"/>
     </row>
     <row r="577" ht="13.65" customHeight="1">
       <c r="A577" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B577" t="s" s="3">
         <v>347</v>
@@ -13693,10 +13689,10 @@
     </row>
     <row r="578" ht="13.65" customHeight="1">
       <c r="A578" t="s" s="3">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B578" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C578" s="3"/>
       <c r="D578" t="s" s="3">
@@ -13707,24 +13703,24 @@
     </row>
     <row r="579" ht="13.65" customHeight="1">
       <c r="A579" t="s" s="3">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B579" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C579" s="3"/>
       <c r="D579" t="s" s="3">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E579" s="4"/>
       <c r="F579" s="4"/>
     </row>
     <row r="580" ht="13.65" customHeight="1">
       <c r="A580" t="s" s="3">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B580" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C580" s="3"/>
       <c r="D580" t="s" s="3">
@@ -13735,105 +13731,105 @@
     </row>
     <row r="581" ht="13.65" customHeight="1">
       <c r="A581" t="s" s="3">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B581" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C581" s="3"/>
       <c r="D581" t="s" s="3">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E581" s="4"/>
       <c r="F581" s="4"/>
     </row>
     <row r="582" ht="13.65" customHeight="1">
       <c r="A582" t="s" s="3">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B582" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C582" s="3"/>
       <c r="D582" t="s" s="3">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E582" s="4"/>
       <c r="F582" s="4"/>
     </row>
     <row r="583" ht="13.65" customHeight="1">
       <c r="A583" t="s" s="3">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B583" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C583" s="3"/>
       <c r="D583" t="s" s="3">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E583" s="4"/>
       <c r="F583" s="4"/>
     </row>
     <row r="584" ht="13.65" customHeight="1">
       <c r="A584" t="s" s="3">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B584" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C584" s="3"/>
       <c r="D584" t="s" s="3">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E584" s="4"/>
       <c r="F584" s="4"/>
     </row>
     <row r="585" ht="13.65" customHeight="1">
       <c r="A585" t="s" s="3">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B585" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C585" s="3"/>
       <c r="D585" t="s" s="3">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E585" s="4"/>
       <c r="F585" s="4"/>
     </row>
     <row r="586" ht="13.65" customHeight="1">
       <c r="A586" t="s" s="3">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B586" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C586" s="3"/>
       <c r="D586" t="s" s="3">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E586" s="4"/>
       <c r="F586" s="4"/>
     </row>
     <row r="587" ht="13.65" customHeight="1">
       <c r="A587" t="s" s="3">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B587" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C587" s="3"/>
       <c r="D587" t="s" s="3">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E587" s="4"/>
       <c r="F587" s="4"/>
     </row>
     <row r="588" ht="13.65" customHeight="1">
       <c r="A588" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B588" t="s" s="3">
         <v>444</v>
@@ -13847,21 +13843,21 @@
     </row>
     <row r="589" ht="13.65" customHeight="1">
       <c r="A589" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B589" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C589" s="3"/>
       <c r="D589" t="s" s="3">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E589" s="4"/>
       <c r="F589" s="4"/>
     </row>
     <row r="590" ht="13.65" customHeight="1">
       <c r="A590" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B590" t="s" s="3">
         <v>444</v>
@@ -13875,63 +13871,63 @@
     </row>
     <row r="591" ht="13.65" customHeight="1">
       <c r="A591" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B591" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C591" s="3"/>
       <c r="D591" t="s" s="3">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E591" s="4"/>
       <c r="F591" s="4"/>
     </row>
     <row r="592" ht="13.65" customHeight="1">
       <c r="A592" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B592" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C592" s="3"/>
       <c r="D592" t="s" s="3">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E592" s="4"/>
       <c r="F592" s="4"/>
     </row>
     <row r="593" ht="13.65" customHeight="1">
       <c r="A593" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B593" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C593" s="3"/>
       <c r="D593" t="s" s="3">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E593" s="4"/>
       <c r="F593" s="4"/>
     </row>
     <row r="594" ht="13.65" customHeight="1">
       <c r="A594" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B594" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C594" s="3"/>
       <c r="D594" t="s" s="3">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E594" s="4"/>
       <c r="F594" s="4"/>
     </row>
     <row r="595" ht="13.65" customHeight="1">
       <c r="A595" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B595" t="s" s="3">
         <v>444</v>
@@ -13945,21 +13941,21 @@
     </row>
     <row r="596" ht="13.65" customHeight="1">
       <c r="A596" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B596" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C596" s="3"/>
       <c r="D596" t="s" s="3">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E596" s="4"/>
       <c r="F596" s="4"/>
     </row>
     <row r="597" ht="13.65" customHeight="1">
       <c r="A597" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B597" t="s" s="3">
         <v>444</v>
@@ -13973,7 +13969,7 @@
     </row>
     <row r="598" ht="13.65" customHeight="1">
       <c r="A598" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B598" t="s" s="3">
         <v>444</v>
@@ -13987,7 +13983,7 @@
     </row>
     <row r="599" ht="13.65" customHeight="1">
       <c r="A599" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B599" t="s" s="3">
         <v>444</v>
@@ -14001,7 +13997,7 @@
     </row>
     <row r="600" ht="13.65" customHeight="1">
       <c r="A600" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B600" t="s" s="3">
         <v>444</v>
@@ -14015,35 +14011,35 @@
     </row>
     <row r="601" ht="13.65" customHeight="1">
       <c r="A601" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B601" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C601" s="3"/>
       <c r="D601" t="s" s="3">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E601" s="4"/>
       <c r="F601" s="4"/>
     </row>
     <row r="602" ht="13.65" customHeight="1">
       <c r="A602" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B602" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C602" s="3"/>
       <c r="D602" t="s" s="3">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E602" s="4"/>
       <c r="F602" s="4"/>
     </row>
     <row r="603" ht="13.65" customHeight="1">
       <c r="A603" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B603" t="s" s="3">
         <v>444</v>
@@ -14057,35 +14053,35 @@
     </row>
     <row r="604" ht="13.65" customHeight="1">
       <c r="A604" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B604" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C604" s="3"/>
       <c r="D604" t="s" s="3">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E604" s="4"/>
       <c r="F604" s="4"/>
     </row>
     <row r="605" ht="13.65" customHeight="1">
       <c r="A605" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B605" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C605" s="3"/>
       <c r="D605" t="s" s="3">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E605" s="4"/>
       <c r="F605" s="4"/>
     </row>
     <row r="606" ht="13.65" customHeight="1">
       <c r="A606" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B606" t="s" s="3">
         <v>444</v>
@@ -14099,7 +14095,7 @@
     </row>
     <row r="607" ht="13.65" customHeight="1">
       <c r="A607" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B607" t="s" s="3">
         <v>444</v>
@@ -14113,63 +14109,63 @@
     </row>
     <row r="608" ht="13.65" customHeight="1">
       <c r="A608" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B608" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C608" s="3"/>
       <c r="D608" t="s" s="3">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E608" s="4"/>
       <c r="F608" s="4"/>
     </row>
     <row r="609" ht="13.65" customHeight="1">
       <c r="A609" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B609" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C609" s="3"/>
       <c r="D609" t="s" s="3">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E609" s="4"/>
       <c r="F609" s="4"/>
     </row>
     <row r="610" ht="13.65" customHeight="1">
       <c r="A610" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B610" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C610" s="3"/>
       <c r="D610" t="s" s="3">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E610" s="4"/>
       <c r="F610" s="4"/>
     </row>
     <row r="611" ht="13.65" customHeight="1">
       <c r="A611" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B611" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C611" s="3"/>
       <c r="D611" t="s" s="3">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E611" s="4"/>
       <c r="F611" s="4"/>
     </row>
     <row r="612" ht="13.65" customHeight="1">
       <c r="A612" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B612" t="s" s="3">
         <v>444</v>
@@ -14183,7 +14179,7 @@
     </row>
     <row r="613" ht="13.65" customHeight="1">
       <c r="A613" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B613" t="s" s="3">
         <v>444</v>
@@ -14197,7 +14193,7 @@
     </row>
     <row r="614" ht="13.65" customHeight="1">
       <c r="A614" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B614" t="s" s="3">
         <v>444</v>
@@ -14211,21 +14207,21 @@
     </row>
     <row r="615" ht="13.65" customHeight="1">
       <c r="A615" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B615" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C615" s="3"/>
       <c r="D615" t="s" s="3">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E615" s="4"/>
       <c r="F615" s="4"/>
     </row>
     <row r="616" ht="13.65" customHeight="1">
       <c r="A616" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B616" t="s" s="3">
         <v>444</v>
@@ -14239,105 +14235,105 @@
     </row>
     <row r="617" ht="13.65" customHeight="1">
       <c r="A617" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B617" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C617" s="3"/>
       <c r="D617" t="s" s="3">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E617" s="4"/>
       <c r="F617" s="4"/>
     </row>
     <row r="618" ht="13.65" customHeight="1">
       <c r="A618" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B618" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C618" s="3"/>
       <c r="D618" t="s" s="3">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E618" s="4"/>
       <c r="F618" s="4"/>
     </row>
     <row r="619" ht="13.65" customHeight="1">
       <c r="A619" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B619" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C619" s="3"/>
       <c r="D619" t="s" s="3">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E619" s="4"/>
       <c r="F619" s="4"/>
     </row>
     <row r="620" ht="13.65" customHeight="1">
       <c r="A620" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B620" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C620" s="3"/>
       <c r="D620" t="s" s="3">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E620" s="4"/>
       <c r="F620" s="4"/>
     </row>
     <row r="621" ht="13.65" customHeight="1">
       <c r="A621" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B621" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C621" s="3"/>
       <c r="D621" t="s" s="3">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E621" s="4"/>
       <c r="F621" s="4"/>
     </row>
     <row r="622" ht="13.65" customHeight="1">
       <c r="A622" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B622" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C622" s="3"/>
       <c r="D622" t="s" s="3">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E622" s="4"/>
       <c r="F622" s="4"/>
     </row>
     <row r="623" ht="13.65" customHeight="1">
       <c r="A623" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B623" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C623" s="3"/>
       <c r="D623" t="s" s="3">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E623" s="4"/>
       <c r="F623" s="4"/>
     </row>
     <row r="624" ht="13.65" customHeight="1">
       <c r="A624" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B624" t="s" s="3">
         <v>444</v>
@@ -14351,7 +14347,7 @@
     </row>
     <row r="625" ht="13.65" customHeight="1">
       <c r="A625" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B625" t="s" s="3">
         <v>444</v>
@@ -14365,7 +14361,7 @@
     </row>
     <row r="626" ht="13.65" customHeight="1">
       <c r="A626" t="s" s="3">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B626" t="s" s="3">
         <v>347</v>
@@ -14379,49 +14375,49 @@
     </row>
     <row r="627" ht="13.65" customHeight="1">
       <c r="A627" t="s" s="3">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B627" t="s" s="3">
         <v>347</v>
       </c>
       <c r="C627" s="3"/>
       <c r="D627" t="s" s="3">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E627" s="4"/>
       <c r="F627" s="4"/>
     </row>
     <row r="628" ht="13.65" customHeight="1">
       <c r="A628" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B628" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C628" s="3"/>
       <c r="D628" t="s" s="3">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E628" s="4"/>
       <c r="F628" s="4"/>
     </row>
     <row r="629" ht="13.65" customHeight="1">
       <c r="A629" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B629" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C629" s="3"/>
       <c r="D629" t="s" s="3">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E629" s="4"/>
       <c r="F629" s="4"/>
     </row>
     <row r="630" ht="13.65" customHeight="1">
       <c r="A630" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B630" t="s" s="3">
         <v>178</v>
@@ -14435,21 +14431,21 @@
     </row>
     <row r="631" ht="13.65" customHeight="1">
       <c r="A631" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B631" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C631" s="3"/>
       <c r="D631" t="s" s="3">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E631" s="4"/>
       <c r="F631" s="4"/>
     </row>
     <row r="632" ht="13.65" customHeight="1">
       <c r="A632" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B632" t="s" s="3">
         <v>178</v>
@@ -14463,21 +14459,21 @@
     </row>
     <row r="633" ht="13.65" customHeight="1">
       <c r="A633" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B633" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C633" s="3"/>
       <c r="D633" t="s" s="3">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E633" s="4"/>
       <c r="F633" s="4"/>
     </row>
     <row r="634" ht="13.65" customHeight="1">
       <c r="A634" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B634" t="s" s="3">
         <v>178</v>
@@ -14491,7 +14487,7 @@
     </row>
     <row r="635" ht="13.65" customHeight="1">
       <c r="A635" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B635" t="s" s="3">
         <v>178</v>
@@ -14505,63 +14501,63 @@
     </row>
     <row r="636" ht="13.65" customHeight="1">
       <c r="A636" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B636" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C636" s="3"/>
       <c r="D636" t="s" s="3">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E636" s="4"/>
       <c r="F636" s="4"/>
     </row>
     <row r="637" ht="13.65" customHeight="1">
       <c r="A637" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B637" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C637" s="3"/>
       <c r="D637" t="s" s="3">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E637" s="4"/>
       <c r="F637" s="4"/>
     </row>
     <row r="638" ht="13.65" customHeight="1">
       <c r="A638" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B638" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C638" s="3"/>
       <c r="D638" t="s" s="3">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E638" s="4"/>
       <c r="F638" s="4"/>
     </row>
     <row r="639" ht="13.65" customHeight="1">
       <c r="A639" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B639" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C639" s="3"/>
       <c r="D639" t="s" s="3">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E639" s="4"/>
       <c r="F639" s="4"/>
     </row>
     <row r="640" ht="13.65" customHeight="1">
       <c r="A640" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B640" t="s" s="3">
         <v>178</v>
@@ -14575,35 +14571,35 @@
     </row>
     <row r="641" ht="13.65" customHeight="1">
       <c r="A641" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B641" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C641" s="3"/>
       <c r="D641" t="s" s="3">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E641" s="4"/>
       <c r="F641" s="4"/>
     </row>
     <row r="642" ht="13.65" customHeight="1">
       <c r="A642" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B642" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C642" s="3"/>
       <c r="D642" t="s" s="3">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E642" s="4"/>
       <c r="F642" s="4"/>
     </row>
     <row r="643" ht="13.65" customHeight="1">
       <c r="A643" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B643" t="s" s="3">
         <v>444</v>
@@ -14617,7 +14613,7 @@
     </row>
     <row r="644" ht="13.65" customHeight="1">
       <c r="A644" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B644" t="s" s="3">
         <v>444</v>
@@ -14631,63 +14627,63 @@
     </row>
     <row r="645" ht="13.65" customHeight="1">
       <c r="A645" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B645" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C645" s="3"/>
       <c r="D645" t="s" s="3">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E645" s="4"/>
       <c r="F645" s="4"/>
     </row>
     <row r="646" ht="13.65" customHeight="1">
       <c r="A646" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B646" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C646" s="3"/>
       <c r="D646" t="s" s="3">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E646" s="4"/>
       <c r="F646" s="4"/>
     </row>
     <row r="647" ht="13.65" customHeight="1">
       <c r="A647" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B647" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C647" s="3"/>
       <c r="D647" t="s" s="3">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E647" s="4"/>
       <c r="F647" s="4"/>
     </row>
     <row r="648" ht="13.65" customHeight="1">
       <c r="A648" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B648" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C648" s="3"/>
       <c r="D648" t="s" s="3">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E648" s="4"/>
       <c r="F648" s="4"/>
     </row>
     <row r="649" ht="13.65" customHeight="1">
       <c r="A649" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B649" t="s" s="3">
         <v>444</v>
@@ -14701,21 +14697,21 @@
     </row>
     <row r="650" ht="13.65" customHeight="1">
       <c r="A650" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B650" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C650" s="3"/>
       <c r="D650" t="s" s="3">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E650" s="4"/>
       <c r="F650" s="4"/>
     </row>
     <row r="651" ht="13.65" customHeight="1">
       <c r="A651" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B651" t="s" s="3">
         <v>444</v>
@@ -14729,35 +14725,35 @@
     </row>
     <row r="652" ht="13.65" customHeight="1">
       <c r="A652" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B652" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C652" s="3"/>
       <c r="D652" t="s" s="3">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E652" s="4"/>
       <c r="F652" s="4"/>
     </row>
     <row r="653" ht="13.65" customHeight="1">
       <c r="A653" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B653" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C653" s="3"/>
       <c r="D653" t="s" s="3">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E653" s="4"/>
       <c r="F653" s="4"/>
     </row>
     <row r="654" ht="13.65" customHeight="1">
       <c r="A654" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B654" t="s" s="3">
         <v>444</v>
@@ -14771,63 +14767,63 @@
     </row>
     <row r="655" ht="13.65" customHeight="1">
       <c r="A655" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B655" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C655" s="3"/>
       <c r="D655" t="s" s="3">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E655" s="4"/>
       <c r="F655" s="4"/>
     </row>
     <row r="656" ht="13.65" customHeight="1">
       <c r="A656" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B656" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C656" s="3"/>
       <c r="D656" t="s" s="3">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E656" s="4"/>
       <c r="F656" s="4"/>
     </row>
     <row r="657" ht="13.65" customHeight="1">
       <c r="A657" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B657" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C657" s="3"/>
       <c r="D657" t="s" s="3">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E657" s="4"/>
       <c r="F657" s="4"/>
     </row>
     <row r="658" ht="13.65" customHeight="1">
       <c r="A658" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B658" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C658" s="3"/>
       <c r="D658" t="s" s="3">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E658" s="4"/>
       <c r="F658" s="4"/>
     </row>
     <row r="659" ht="13.65" customHeight="1">
       <c r="A659" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B659" t="s" s="3">
         <v>444</v>
@@ -14841,63 +14837,63 @@
     </row>
     <row r="660" ht="13.65" customHeight="1">
       <c r="A660" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B660" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C660" s="3"/>
       <c r="D660" t="s" s="3">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E660" s="4"/>
       <c r="F660" s="4"/>
     </row>
     <row r="661" ht="13.65" customHeight="1">
       <c r="A661" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B661" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C661" s="3"/>
       <c r="D661" t="s" s="3">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E661" s="4"/>
       <c r="F661" s="4"/>
     </row>
     <row r="662" ht="13.65" customHeight="1">
       <c r="A662" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B662" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C662" s="3"/>
       <c r="D662" t="s" s="3">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E662" s="4"/>
       <c r="F662" s="4"/>
     </row>
     <row r="663" ht="13.65" customHeight="1">
       <c r="A663" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B663" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C663" s="3"/>
       <c r="D663" t="s" s="3">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E663" s="4"/>
       <c r="F663" s="4"/>
     </row>
     <row r="664" ht="13.65" customHeight="1">
       <c r="A664" t="s" s="3">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B664" t="s" s="3">
         <v>444</v>
@@ -14911,7 +14907,7 @@
     </row>
     <row r="665" ht="13.65" customHeight="1">
       <c r="A665" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B665" t="s" s="3">
         <v>178</v>
@@ -14925,7 +14921,7 @@
     </row>
     <row r="666" ht="13.65" customHeight="1">
       <c r="A666" t="s" s="3">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B666" t="s" s="3">
         <v>444</v>
@@ -14939,10 +14935,10 @@
     </row>
     <row r="667" ht="13.65" customHeight="1">
       <c r="A667" t="s" s="3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B667" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C667" s="3"/>
       <c r="D667" t="s" s="3">
@@ -14953,10 +14949,10 @@
     </row>
     <row r="668" ht="13.65" customHeight="1">
       <c r="A668" t="s" s="3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B668" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C668" s="3"/>
       <c r="D668" t="s" s="3">
@@ -14967,10 +14963,10 @@
     </row>
     <row r="669" ht="13.65" customHeight="1">
       <c r="A669" t="s" s="3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B669" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C669" s="3"/>
       <c r="D669" t="s" s="3">
@@ -14981,10 +14977,10 @@
     </row>
     <row r="670" ht="13.65" customHeight="1">
       <c r="A670" t="s" s="3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B670" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C670" s="3"/>
       <c r="D670" t="s" s="3">
@@ -14995,24 +14991,24 @@
     </row>
     <row r="671" ht="13.65" customHeight="1">
       <c r="A671" t="s" s="3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B671" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C671" s="3"/>
       <c r="D671" t="s" s="3">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E671" s="4"/>
       <c r="F671" s="4"/>
     </row>
     <row r="672" ht="13.65" customHeight="1">
       <c r="A672" t="s" s="3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B672" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C672" s="3"/>
       <c r="D672" t="s" s="3">
@@ -15023,10 +15019,10 @@
     </row>
     <row r="673" ht="13.65" customHeight="1">
       <c r="A673" t="s" s="3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B673" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C673" s="3"/>
       <c r="D673" t="s" s="3">
@@ -15037,10 +15033,10 @@
     </row>
     <row r="674" ht="13.65" customHeight="1">
       <c r="A674" t="s" s="3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B674" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C674" s="3"/>
       <c r="D674" t="s" s="3">
@@ -15051,24 +15047,24 @@
     </row>
     <row r="675" ht="13.65" customHeight="1">
       <c r="A675" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B675" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C675" s="3"/>
       <c r="D675" t="s" s="3">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E675" s="4"/>
       <c r="F675" s="4"/>
     </row>
     <row r="676" ht="13.65" customHeight="1">
       <c r="A676" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B676" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C676" s="3"/>
       <c r="D676" t="s" s="3">
@@ -15079,66 +15075,66 @@
     </row>
     <row r="677" ht="13.65" customHeight="1">
       <c r="A677" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B677" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C677" s="3"/>
       <c r="D677" t="s" s="3">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E677" s="4"/>
       <c r="F677" s="4"/>
     </row>
     <row r="678" ht="13.65" customHeight="1">
       <c r="A678" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B678" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C678" s="3"/>
       <c r="D678" t="s" s="3">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E678" s="4"/>
       <c r="F678" s="4"/>
     </row>
     <row r="679" ht="13.65" customHeight="1">
       <c r="A679" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B679" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C679" s="3"/>
       <c r="D679" t="s" s="3">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E679" s="4"/>
       <c r="F679" s="4"/>
     </row>
     <row r="680" ht="13.65" customHeight="1">
       <c r="A680" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B680" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C680" s="3"/>
       <c r="D680" t="s" s="3">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E680" s="4"/>
       <c r="F680" s="4"/>
     </row>
     <row r="681" ht="13.65" customHeight="1">
       <c r="A681" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B681" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C681" s="3"/>
       <c r="D681" t="s" s="3">
@@ -15149,66 +15145,66 @@
     </row>
     <row r="682" ht="13.65" customHeight="1">
       <c r="A682" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B682" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C682" s="3"/>
       <c r="D682" t="s" s="3">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E682" s="4"/>
       <c r="F682" s="4"/>
     </row>
     <row r="683" ht="13.65" customHeight="1">
       <c r="A683" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B683" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C683" s="3"/>
       <c r="D683" t="s" s="3">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E683" s="4"/>
       <c r="F683" s="4"/>
     </row>
     <row r="684" ht="13.65" customHeight="1">
       <c r="A684" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B684" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C684" s="3"/>
       <c r="D684" t="s" s="3">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E684" s="4"/>
       <c r="F684" s="4"/>
     </row>
     <row r="685" ht="13.65" customHeight="1">
       <c r="A685" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B685" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C685" s="3"/>
       <c r="D685" t="s" s="3">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E685" s="4"/>
       <c r="F685" s="4"/>
     </row>
     <row r="686" ht="13.65" customHeight="1">
       <c r="A686" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B686" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C686" s="3"/>
       <c r="D686" t="s" s="3">
@@ -15219,10 +15215,10 @@
     </row>
     <row r="687" ht="13.65" customHeight="1">
       <c r="A687" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B687" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C687" s="3"/>
       <c r="D687" t="s" s="3">
@@ -15233,10 +15229,10 @@
     </row>
     <row r="688" ht="13.65" customHeight="1">
       <c r="A688" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B688" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C688" s="3"/>
       <c r="D688" t="s" s="3">
@@ -15247,10 +15243,10 @@
     </row>
     <row r="689" ht="13.65" customHeight="1">
       <c r="A689" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B689" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C689" s="3"/>
       <c r="D689" t="s" s="3">
@@ -15261,10 +15257,10 @@
     </row>
     <row r="690" ht="13.65" customHeight="1">
       <c r="A690" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B690" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C690" s="3"/>
       <c r="D690" t="s" s="3">
@@ -15275,38 +15271,38 @@
     </row>
     <row r="691" ht="13.65" customHeight="1">
       <c r="A691" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B691" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C691" s="3"/>
       <c r="D691" t="s" s="3">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E691" s="4"/>
       <c r="F691" s="4"/>
     </row>
     <row r="692" ht="13.65" customHeight="1">
       <c r="A692" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B692" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C692" s="3"/>
       <c r="D692" t="s" s="3">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E692" s="4"/>
       <c r="F692" s="4"/>
     </row>
     <row r="693" ht="13.65" customHeight="1">
       <c r="A693" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B693" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C693" s="3"/>
       <c r="D693" t="s" s="3">
@@ -15317,38 +15313,38 @@
     </row>
     <row r="694" ht="13.65" customHeight="1">
       <c r="A694" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B694" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C694" s="3"/>
       <c r="D694" t="s" s="3">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E694" s="4"/>
       <c r="F694" s="4"/>
     </row>
     <row r="695" ht="13.65" customHeight="1">
       <c r="A695" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B695" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C695" s="3"/>
       <c r="D695" t="s" s="3">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E695" s="4"/>
       <c r="F695" s="4"/>
     </row>
     <row r="696" ht="13.65" customHeight="1">
       <c r="A696" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B696" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C696" s="3"/>
       <c r="D696" t="s" s="3">
@@ -15359,10 +15355,10 @@
     </row>
     <row r="697" ht="13.65" customHeight="1">
       <c r="A697" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B697" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C697" s="3"/>
       <c r="D697" t="s" s="3">
@@ -15373,10 +15369,10 @@
     </row>
     <row r="698" ht="13.65" customHeight="1">
       <c r="A698" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B698" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C698" s="3"/>
       <c r="D698" t="s" s="3">
@@ -15387,38 +15383,38 @@
     </row>
     <row r="699" ht="13.65" customHeight="1">
       <c r="A699" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B699" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C699" s="3"/>
       <c r="D699" t="s" s="3">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E699" s="4"/>
       <c r="F699" s="4"/>
     </row>
     <row r="700" ht="13.65" customHeight="1">
       <c r="A700" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B700" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C700" s="3"/>
       <c r="D700" t="s" s="3">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E700" s="4"/>
       <c r="F700" s="4"/>
     </row>
     <row r="701" ht="13.65" customHeight="1">
       <c r="A701" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B701" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C701" s="3"/>
       <c r="D701" t="s" s="3">
@@ -15429,10 +15425,10 @@
     </row>
     <row r="702" ht="13.65" customHeight="1">
       <c r="A702" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B702" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C702" s="3"/>
       <c r="D702" t="s" s="3">
@@ -15443,24 +15439,24 @@
     </row>
     <row r="703" ht="13.65" customHeight="1">
       <c r="A703" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B703" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C703" s="3"/>
       <c r="D703" t="s" s="3">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E703" s="4"/>
       <c r="F703" s="4"/>
     </row>
     <row r="704" ht="13.65" customHeight="1">
       <c r="A704" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B704" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C704" s="3"/>
       <c r="D704" t="s" s="3">
@@ -15471,24 +15467,24 @@
     </row>
     <row r="705" ht="13.65" customHeight="1">
       <c r="A705" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B705" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C705" s="3"/>
       <c r="D705" t="s" s="3">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E705" s="4"/>
       <c r="F705" s="4"/>
     </row>
     <row r="706" ht="13.65" customHeight="1">
       <c r="A706" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B706" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C706" s="3"/>
       <c r="D706" t="s" s="3">
@@ -15499,38 +15495,38 @@
     </row>
     <row r="707" ht="13.65" customHeight="1">
       <c r="A707" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B707" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C707" s="3"/>
       <c r="D707" t="s" s="3">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E707" s="4"/>
       <c r="F707" s="4"/>
     </row>
     <row r="708" ht="13.65" customHeight="1">
       <c r="A708" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B708" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C708" s="3"/>
       <c r="D708" t="s" s="3">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E708" s="4"/>
       <c r="F708" s="4"/>
     </row>
     <row r="709" ht="13.65" customHeight="1">
       <c r="A709" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B709" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C709" s="3"/>
       <c r="D709" t="s" s="3">
@@ -15541,24 +15537,24 @@
     </row>
     <row r="710" ht="13.65" customHeight="1">
       <c r="A710" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B710" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C710" s="3"/>
       <c r="D710" t="s" s="3">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E710" s="4"/>
       <c r="F710" s="4"/>
     </row>
     <row r="711" ht="13.65" customHeight="1">
       <c r="A711" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B711" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C711" s="3"/>
       <c r="D711" t="s" s="3">
@@ -15569,10 +15565,10 @@
     </row>
     <row r="712" ht="13.65" customHeight="1">
       <c r="A712" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B712" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C712" s="3"/>
       <c r="D712" t="s" s="3">
@@ -15583,10 +15579,10 @@
     </row>
     <row r="713" ht="13.65" customHeight="1">
       <c r="A713" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B713" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C713" s="3"/>
       <c r="D713" t="s" s="3">
@@ -15597,10 +15593,10 @@
     </row>
     <row r="714" ht="13.65" customHeight="1">
       <c r="A714" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B714" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C714" s="3"/>
       <c r="D714" t="s" s="3">
@@ -15611,10 +15607,10 @@
     </row>
     <row r="715" ht="13.65" customHeight="1">
       <c r="A715" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B715" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C715" s="3"/>
       <c r="D715" t="s" s="3">
@@ -15625,10 +15621,10 @@
     </row>
     <row r="716" ht="13.65" customHeight="1">
       <c r="A716" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B716" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C716" s="3"/>
       <c r="D716" t="s" s="3">
@@ -15639,10 +15635,10 @@
     </row>
     <row r="717" ht="13.65" customHeight="1">
       <c r="A717" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B717" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C717" s="3"/>
       <c r="D717" t="s" s="3">
@@ -15653,10 +15649,10 @@
     </row>
     <row r="718" ht="13.65" customHeight="1">
       <c r="A718" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B718" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C718" s="3"/>
       <c r="D718" t="s" s="3">
@@ -15667,24 +15663,24 @@
     </row>
     <row r="719" ht="13.65" customHeight="1">
       <c r="A719" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B719" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C719" s="3"/>
       <c r="D719" t="s" s="3">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E719" s="4"/>
       <c r="F719" s="4"/>
     </row>
     <row r="720" ht="13.65" customHeight="1">
       <c r="A720" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B720" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C720" s="3"/>
       <c r="D720" t="s" s="3">
@@ -15695,38 +15691,38 @@
     </row>
     <row r="721" ht="13.65" customHeight="1">
       <c r="A721" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B721" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C721" s="3"/>
       <c r="D721" t="s" s="3">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E721" s="4"/>
       <c r="F721" s="4"/>
     </row>
     <row r="722" ht="13.65" customHeight="1">
       <c r="A722" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B722" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C722" s="3"/>
       <c r="D722" t="s" s="3">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E722" s="4"/>
       <c r="F722" s="4"/>
     </row>
     <row r="723" ht="13.65" customHeight="1">
       <c r="A723" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B723" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C723" s="3"/>
       <c r="D723" t="s" s="3">
@@ -15737,24 +15733,24 @@
     </row>
     <row r="724" ht="13.65" customHeight="1">
       <c r="A724" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B724" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C724" s="3"/>
       <c r="D724" t="s" s="3">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E724" s="4"/>
       <c r="F724" s="4"/>
     </row>
     <row r="725" ht="13.65" customHeight="1">
       <c r="A725" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B725" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C725" s="3"/>
       <c r="D725" t="s" s="3">
@@ -15765,94 +15761,94 @@
     </row>
     <row r="726" ht="13.65" customHeight="1">
       <c r="A726" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B726" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C726" s="3"/>
       <c r="D726" t="s" s="3">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E726" s="4"/>
       <c r="F726" s="4"/>
     </row>
     <row r="727" ht="13.65" customHeight="1">
       <c r="A727" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B727" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C727" s="3"/>
       <c r="D727" t="s" s="3">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E727" s="4"/>
       <c r="F727" s="4"/>
     </row>
     <row r="728" ht="13.65" customHeight="1">
       <c r="A728" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B728" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C728" s="3"/>
       <c r="D728" t="s" s="3">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E728" s="4"/>
       <c r="F728" s="4"/>
     </row>
     <row r="729" ht="13.65" customHeight="1">
       <c r="A729" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B729" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C729" s="3"/>
       <c r="D729" t="s" s="3">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E729" s="4"/>
       <c r="F729" s="4"/>
     </row>
     <row r="730" ht="13.65" customHeight="1">
       <c r="A730" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B730" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C730" s="3"/>
       <c r="D730" t="s" s="3">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E730" s="4"/>
       <c r="F730" s="4"/>
     </row>
     <row r="731" ht="13.65" customHeight="1">
       <c r="A731" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B731" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C731" s="3"/>
       <c r="D731" t="s" s="3">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E731" s="4"/>
       <c r="F731" s="4"/>
     </row>
     <row r="732" ht="13.65" customHeight="1">
       <c r="A732" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B732" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C732" s="3"/>
       <c r="D732" t="s" s="3">
@@ -15863,66 +15859,66 @@
     </row>
     <row r="733" ht="13.65" customHeight="1">
       <c r="A733" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B733" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C733" s="3"/>
       <c r="D733" t="s" s="3">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E733" s="4"/>
       <c r="F733" s="4"/>
     </row>
     <row r="734" ht="13.65" customHeight="1">
       <c r="A734" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B734" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C734" s="3"/>
       <c r="D734" t="s" s="3">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E734" s="4"/>
       <c r="F734" s="4"/>
     </row>
     <row r="735" ht="13.65" customHeight="1">
       <c r="A735" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B735" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C735" s="3"/>
       <c r="D735" t="s" s="3">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E735" s="4"/>
       <c r="F735" s="4"/>
     </row>
     <row r="736" ht="13.65" customHeight="1">
       <c r="A736" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B736" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C736" s="3"/>
       <c r="D736" t="s" s="3">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E736" s="4"/>
       <c r="F736" s="4"/>
     </row>
     <row r="737" ht="13.65" customHeight="1">
       <c r="A737" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B737" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C737" s="3"/>
       <c r="D737" t="s" s="3">
@@ -15933,10 +15929,10 @@
     </row>
     <row r="738" ht="13.65" customHeight="1">
       <c r="A738" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B738" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C738" s="3"/>
       <c r="D738" t="s" s="3">
@@ -15947,108 +15943,108 @@
     </row>
     <row r="739" ht="13.65" customHeight="1">
       <c r="A739" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B739" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C739" s="3"/>
       <c r="D739" t="s" s="3">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E739" s="4"/>
       <c r="F739" s="4"/>
     </row>
     <row r="740" ht="13.65" customHeight="1">
       <c r="A740" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B740" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C740" s="3"/>
       <c r="D740" t="s" s="3">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E740" s="4"/>
       <c r="F740" s="4"/>
     </row>
     <row r="741" ht="13.65" customHeight="1">
       <c r="A741" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B741" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C741" s="3"/>
       <c r="D741" t="s" s="3">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E741" s="4"/>
       <c r="F741" s="4"/>
     </row>
     <row r="742" ht="13.65" customHeight="1">
       <c r="A742" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B742" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C742" s="3"/>
       <c r="D742" t="s" s="3">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E742" s="4"/>
       <c r="F742" s="4"/>
     </row>
     <row r="743" ht="13.65" customHeight="1">
       <c r="A743" t="s" s="3">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B743" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C743" s="3"/>
       <c r="D743" t="s" s="3">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E743" s="4"/>
       <c r="F743" s="4"/>
     </row>
     <row r="744" ht="13.65" customHeight="1">
       <c r="A744" t="s" s="3">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B744" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C744" s="3"/>
       <c r="D744" t="s" s="3">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E744" s="4"/>
       <c r="F744" s="4"/>
     </row>
     <row r="745" ht="13.65" customHeight="1">
       <c r="A745" t="s" s="3">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B745" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C745" s="3"/>
       <c r="D745" t="s" s="3">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E745" s="4"/>
       <c r="F745" s="4"/>
     </row>
     <row r="746" ht="13.65" customHeight="1">
       <c r="A746" t="s" s="3">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B746" t="s" s="3">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="C746" s="3"/>
       <c r="D746" t="s" s="3">
@@ -16059,10 +16055,10 @@
     </row>
     <row r="747" ht="13.65" customHeight="1">
       <c r="A747" t="s" s="3">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B747" t="s" s="3">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="C747" s="3"/>
       <c r="D747" t="s" s="3">
@@ -16073,10 +16069,10 @@
     </row>
     <row r="748" ht="13.65" customHeight="1">
       <c r="A748" t="s" s="3">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B748" t="s" s="3">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="C748" s="3"/>
       <c r="D748" t="s" s="3">
@@ -16162,7 +16158,7 @@
       </c>
       <c r="C754" s="3"/>
       <c r="D754" t="s" s="3">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E754" s="4"/>
       <c r="F754" s="4"/>
@@ -16172,7 +16168,7 @@
         <v>624</v>
       </c>
       <c r="B755" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C755" s="3"/>
       <c r="D755" t="s" s="3">
@@ -16186,7 +16182,7 @@
         <v>624</v>
       </c>
       <c r="B756" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C756" s="3"/>
       <c r="D756" t="s" s="3">
@@ -16200,7 +16196,7 @@
         <v>624</v>
       </c>
       <c r="B757" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C757" s="3"/>
       <c r="D757" t="s" s="3">
@@ -16214,7 +16210,7 @@
         <v>624</v>
       </c>
       <c r="B758" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C758" s="3"/>
       <c r="D758" t="s" s="3">
@@ -16470,7 +16466,7 @@
       </c>
       <c r="C776" s="3"/>
       <c r="D776" t="s" s="3">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E776" s="4"/>
       <c r="F776" s="4"/>
@@ -16624,7 +16620,7 @@
       </c>
       <c r="C787" s="3"/>
       <c r="D787" t="s" s="3">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E787" s="4"/>
       <c r="F787" s="4"/>
@@ -16680,7 +16676,7 @@
       </c>
       <c r="C791" s="3"/>
       <c r="D791" t="s" s="3">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E791" s="4"/>
       <c r="F791" s="4"/>
@@ -16722,7 +16718,7 @@
       </c>
       <c r="C794" s="3"/>
       <c r="D794" t="s" s="3">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E794" s="4"/>
       <c r="F794" s="4"/>
@@ -16890,7 +16886,7 @@
       </c>
       <c r="C806" s="3"/>
       <c r="D806" t="s" s="3">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E806" s="4"/>
       <c r="F806" s="4"/>
@@ -17072,7 +17068,7 @@
       </c>
       <c r="C819" s="3"/>
       <c r="D819" t="s" s="3">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E819" s="4"/>
       <c r="F819" s="4"/>
@@ -17310,7 +17306,7 @@
       </c>
       <c r="C836" s="3"/>
       <c r="D836" t="s" s="3">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E836" s="4"/>
       <c r="F836" s="4"/>
@@ -17422,7 +17418,7 @@
       </c>
       <c r="C844" s="3"/>
       <c r="D844" t="s" s="3">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E844" s="4"/>
       <c r="F844" s="4"/>
@@ -17716,7 +17712,7 @@
       </c>
       <c r="C865" s="3"/>
       <c r="D865" t="s" s="3">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E865" s="4"/>
       <c r="F865" s="4"/>
@@ -17866,7 +17862,7 @@
         <v>699</v>
       </c>
       <c r="B876" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C876" s="3"/>
       <c r="D876" t="s" s="3">
@@ -17908,7 +17904,7 @@
         <v>705</v>
       </c>
       <c r="B879" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C879" s="3"/>
       <c r="D879" t="s" s="3">
@@ -17922,7 +17918,7 @@
         <v>705</v>
       </c>
       <c r="B880" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C880" s="3"/>
       <c r="D880" t="s" s="3">
@@ -17936,7 +17932,7 @@
         <v>705</v>
       </c>
       <c r="B881" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C881" s="3"/>
       <c r="D881" t="s" s="3">
@@ -17950,7 +17946,7 @@
         <v>705</v>
       </c>
       <c r="B882" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C882" s="3"/>
       <c r="D882" t="s" s="3">
@@ -17964,7 +17960,7 @@
         <v>705</v>
       </c>
       <c r="B883" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C883" s="3"/>
       <c r="D883" t="s" s="3">
@@ -17978,7 +17974,7 @@
         <v>705</v>
       </c>
       <c r="B884" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C884" s="3"/>
       <c r="D884" t="s" s="3">
@@ -17992,7 +17988,7 @@
         <v>705</v>
       </c>
       <c r="B885" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C885" s="3"/>
       <c r="D885" t="s" s="3">
@@ -18006,7 +18002,7 @@
         <v>705</v>
       </c>
       <c r="B886" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C886" s="3"/>
       <c r="D886" t="s" s="3">
@@ -18020,7 +18016,7 @@
         <v>705</v>
       </c>
       <c r="B887" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C887" s="3"/>
       <c r="D887" t="s" s="3">
@@ -18034,11 +18030,11 @@
         <v>705</v>
       </c>
       <c r="B888" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C888" s="3"/>
       <c r="D888" t="s" s="3">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E888" s="4"/>
       <c r="F888" s="4"/>
@@ -18048,7 +18044,7 @@
         <v>705</v>
       </c>
       <c r="B889" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C889" s="3"/>
       <c r="D889" t="s" s="3">
@@ -18062,7 +18058,7 @@
         <v>705</v>
       </c>
       <c r="B890" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C890" s="3"/>
       <c r="D890" t="s" s="3">
@@ -18076,7 +18072,7 @@
         <v>705</v>
       </c>
       <c r="B891" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C891" s="3"/>
       <c r="D891" t="s" s="3">
@@ -18090,7 +18086,7 @@
         <v>705</v>
       </c>
       <c r="B892" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C892" s="3"/>
       <c r="D892" t="s" s="3">
@@ -18104,7 +18100,7 @@
         <v>705</v>
       </c>
       <c r="B893" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C893" s="3"/>
       <c r="D893" t="s" s="3">
@@ -18118,7 +18114,7 @@
         <v>705</v>
       </c>
       <c r="B894" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C894" s="3"/>
       <c r="D894" t="s" s="3">
@@ -18132,7 +18128,7 @@
         <v>705</v>
       </c>
       <c r="B895" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C895" s="3"/>
       <c r="D895" t="s" s="3">
@@ -18146,7 +18142,7 @@
         <v>705</v>
       </c>
       <c r="B896" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C896" s="3"/>
       <c r="D896" t="s" s="3">
@@ -18160,7 +18156,7 @@
         <v>705</v>
       </c>
       <c r="B897" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C897" s="3"/>
       <c r="D897" t="s" s="3">
@@ -18304,7 +18300,7 @@
       </c>
       <c r="C907" s="3"/>
       <c r="D907" t="s" s="3">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E907" s="4"/>
       <c r="F907" s="4"/>
@@ -18416,7 +18412,7 @@
       </c>
       <c r="C915" s="3"/>
       <c r="D915" t="s" s="3">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E915" s="4"/>
       <c r="F915" s="4"/>
@@ -18514,7 +18510,7 @@
       </c>
       <c r="C922" s="3"/>
       <c r="D922" t="s" s="3">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E922" s="4"/>
       <c r="F922" s="4"/>
@@ -18906,7 +18902,7 @@
       </c>
       <c r="C950" s="3"/>
       <c r="D950" t="s" s="3">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E950" s="4"/>
       <c r="F950" s="4"/>
@@ -18990,7 +18986,7 @@
       </c>
       <c r="C956" s="3"/>
       <c r="D956" t="s" s="3">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E956" s="4"/>
       <c r="F956" s="4"/>
@@ -19088,7 +19084,7 @@
       </c>
       <c r="C963" s="3"/>
       <c r="D963" t="s" s="3">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E963" s="4"/>
       <c r="F963" s="4"/>
@@ -19102,7 +19098,7 @@
       </c>
       <c r="C964" s="3"/>
       <c r="D964" t="s" s="3">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E964" s="4"/>
       <c r="F964" s="4"/>
@@ -19284,7 +19280,7 @@
       </c>
       <c r="C977" s="3"/>
       <c r="D977" t="s" s="3">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E977" s="4"/>
       <c r="F977" s="4"/>
@@ -19361,7 +19357,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="5" width="12.6719" style="5" customWidth="1"/>
@@ -19421,7 +19417,7 @@
         <v>766</v>
       </c>
       <c r="C4" t="s" s="3">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="D4" t="s" s="3">
         <v>767</v>
@@ -19436,7 +19432,7 @@
         <v>769</v>
       </c>
       <c r="C5" t="s" s="3">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="D5" t="s" s="3">
         <v>767</v>
@@ -19445,13 +19441,13 @@
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" t="s" s="7">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B6" t="s" s="7">
         <v>770</v>
       </c>
       <c r="C6" t="s" s="7">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="D6" t="s" s="7">
         <v>767</v>
@@ -19460,13 +19456,13 @@
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" t="s" s="3">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B7" t="s" s="3">
         <v>771</v>
       </c>
       <c r="C7" t="s" s="3">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="D7" t="s" s="3">
         <v>767</v>
@@ -19481,7 +19477,7 @@
         <v>772</v>
       </c>
       <c r="C8" t="s" s="7">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="D8" t="s" s="7">
         <v>767</v>
@@ -19496,7 +19492,7 @@
         <v>769</v>
       </c>
       <c r="C9" t="s" s="7">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="D9" t="s" s="7">
         <v>767</v>
@@ -19565,7 +19561,7 @@
     </row>
     <row r="14" ht="13.65" customHeight="1">
       <c r="A14" t="s" s="3">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B14" t="s" s="3">
         <v>779</v>
@@ -19610,7 +19606,7 @@
     </row>
     <row r="17" ht="13.65" customHeight="1">
       <c r="A17" t="s" s="3">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B17" t="s" s="3">
         <v>784</v>
@@ -19625,7 +19621,7 @@
     </row>
     <row r="18" ht="13.65" customHeight="1">
       <c r="A18" t="s" s="3">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B18" t="s" s="3">
         <v>785</v>
@@ -19781,7 +19777,7 @@
         <v>796</v>
       </c>
       <c r="C28" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D28" t="s" s="3">
         <v>767</v>
@@ -19796,7 +19792,7 @@
         <v>798</v>
       </c>
       <c r="C29" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D29" t="s" s="3">
         <v>767</v>
@@ -19811,7 +19807,7 @@
         <v>800</v>
       </c>
       <c r="C30" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D30" t="s" s="3">
         <v>767</v>
@@ -19826,7 +19822,7 @@
         <v>801</v>
       </c>
       <c r="C31" t="s" s="6">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D31" t="s" s="6">
         <v>767</v>
@@ -19841,7 +19837,7 @@
         <v>802</v>
       </c>
       <c r="C32" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D32" t="s" s="3">
         <v>767</v>
@@ -19856,7 +19852,7 @@
         <v>804</v>
       </c>
       <c r="C33" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D33" t="s" s="3">
         <v>767</v>
@@ -19865,13 +19861,13 @@
     </row>
     <row r="34" ht="13.65" customHeight="1">
       <c r="A34" t="s" s="3">
+        <v>619</v>
+      </c>
+      <c r="B34" t="s" s="3">
         <v>805</v>
       </c>
-      <c r="B34" t="s" s="3">
-        <v>806</v>
-      </c>
       <c r="C34" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D34" t="s" s="3">
         <v>767</v>
@@ -19880,13 +19876,13 @@
     </row>
     <row r="35" ht="13.65" customHeight="1">
       <c r="A35" t="s" s="3">
+        <v>806</v>
+      </c>
+      <c r="B35" t="s" s="3">
         <v>807</v>
       </c>
-      <c r="B35" t="s" s="3">
-        <v>808</v>
-      </c>
       <c r="C35" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D35" t="s" s="3">
         <v>767</v>
@@ -19895,13 +19891,13 @@
     </row>
     <row r="36" ht="13.65" customHeight="1">
       <c r="A36" t="s" s="3">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B36" t="s" s="3">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C36" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D36" t="s" s="3">
         <v>767</v>
@@ -19910,13 +19906,13 @@
     </row>
     <row r="37" ht="13.65" customHeight="1">
       <c r="A37" t="s" s="7">
+        <v>809</v>
+      </c>
+      <c r="B37" t="s" s="7">
         <v>810</v>
       </c>
-      <c r="B37" t="s" s="7">
-        <v>811</v>
-      </c>
       <c r="C37" t="s" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D37" t="s" s="7">
         <v>767</v>
@@ -19925,13 +19921,13 @@
     </row>
     <row r="38" ht="13.65" customHeight="1">
       <c r="A38" t="s" s="3">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B38" t="s" s="3">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C38" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D38" t="s" s="3">
         <v>767</v>
@@ -19943,10 +19939,10 @@
         <v>624</v>
       </c>
       <c r="B39" t="s" s="7">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C39" t="s" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D39" t="s" s="7">
         <v>767</v>
@@ -19958,10 +19954,10 @@
         <v>699</v>
       </c>
       <c r="B40" t="s" s="3">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C40" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D40" t="s" s="3">
         <v>767</v>
@@ -19973,10 +19969,10 @@
         <v>705</v>
       </c>
       <c r="B41" t="s" s="7">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C41" t="s" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D41" t="s" s="7">
         <v>767</v>
@@ -19991,7 +19987,7 @@
         <v>804</v>
       </c>
       <c r="C42" t="s" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D42" t="s" s="7">
         <v>767</v>
@@ -20000,13 +19996,13 @@
     </row>
     <row r="43" ht="13.65" customHeight="1">
       <c r="A43" t="s" s="6">
+        <v>815</v>
+      </c>
+      <c r="B43" t="s" s="6">
         <v>816</v>
       </c>
-      <c r="B43" t="s" s="6">
-        <v>817</v>
-      </c>
       <c r="C43" t="s" s="6">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D43" t="s" s="6">
         <v>767</v>
@@ -20015,13 +20011,13 @@
     </row>
     <row r="44" ht="13.65" customHeight="1">
       <c r="A44" t="s" s="3">
+        <v>817</v>
+      </c>
+      <c r="B44" t="s" s="3">
         <v>818</v>
       </c>
-      <c r="B44" t="s" s="3">
-        <v>819</v>
-      </c>
       <c r="C44" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D44" t="s" s="3">
         <v>767</v>
@@ -20030,13 +20026,13 @@
     </row>
     <row r="45" ht="13.65" customHeight="1">
       <c r="A45" t="s" s="3">
+        <v>819</v>
+      </c>
+      <c r="B45" t="s" s="3">
         <v>820</v>
       </c>
-      <c r="B45" t="s" s="3">
-        <v>821</v>
-      </c>
       <c r="C45" t="s" s="3">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D45" t="s" s="3">
         <v>767</v>
@@ -20045,13 +20041,13 @@
     </row>
     <row r="46" ht="13.65" customHeight="1">
       <c r="A46" t="s" s="7">
+        <v>821</v>
+      </c>
+      <c r="B46" t="s" s="7">
         <v>822</v>
       </c>
-      <c r="B46" t="s" s="7">
-        <v>823</v>
-      </c>
       <c r="C46" t="s" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D46" t="s" s="7">
         <v>767</v>
@@ -20060,13 +20056,13 @@
     </row>
     <row r="47" ht="13.65" customHeight="1">
       <c r="A47" t="s" s="7">
+        <v>817</v>
+      </c>
+      <c r="B47" t="s" s="7">
         <v>818</v>
       </c>
-      <c r="B47" t="s" s="7">
-        <v>819</v>
-      </c>
       <c r="C47" t="s" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D47" t="s" s="7">
         <v>767</v>
@@ -20075,10 +20071,10 @@
     </row>
     <row r="48" ht="13.65" customHeight="1">
       <c r="A48" t="s" s="3">
+        <v>823</v>
+      </c>
+      <c r="B48" t="s" s="3">
         <v>824</v>
-      </c>
-      <c r="B48" t="s" s="3">
-        <v>825</v>
       </c>
       <c r="C48" t="s" s="3">
         <v>347</v>
@@ -20093,7 +20089,7 @@
         <v>346</v>
       </c>
       <c r="B49" t="s" s="3">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C49" t="s" s="3">
         <v>347</v>
@@ -20105,10 +20101,10 @@
     </row>
     <row r="50" ht="13.65" customHeight="1">
       <c r="A50" t="s" s="3">
+        <v>826</v>
+      </c>
+      <c r="B50" t="s" s="3">
         <v>827</v>
-      </c>
-      <c r="B50" t="s" s="3">
-        <v>828</v>
       </c>
       <c r="C50" t="s" s="3">
         <v>347</v>
@@ -20120,10 +20116,10 @@
     </row>
     <row r="51" ht="13.65" customHeight="1">
       <c r="A51" t="s" s="3">
+        <v>828</v>
+      </c>
+      <c r="B51" t="s" s="3">
         <v>829</v>
-      </c>
-      <c r="B51" t="s" s="3">
-        <v>830</v>
       </c>
       <c r="C51" t="s" s="3">
         <v>347</v>
@@ -20135,10 +20131,10 @@
     </row>
     <row r="52" ht="13.65" customHeight="1">
       <c r="A52" t="s" s="3">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="3">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C52" t="s" s="3">
         <v>347</v>
@@ -20150,10 +20146,10 @@
     </row>
     <row r="53" ht="13.65" customHeight="1">
       <c r="A53" t="s" s="3">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B53" t="s" s="3">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C53" t="s" s="3">
         <v>347</v>
@@ -20168,7 +20164,7 @@
         <v>617</v>
       </c>
       <c r="B54" t="s" s="3">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C54" t="s" s="3">
         <v>347</v>
@@ -20183,7 +20179,7 @@
         <v>622</v>
       </c>
       <c r="B55" t="s" s="3">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C55" t="s" s="3">
         <v>347</v>
@@ -20198,7 +20194,7 @@
         <v>623</v>
       </c>
       <c r="B56" t="s" s="3">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C56" t="s" s="3">
         <v>347</v>
@@ -20213,7 +20209,7 @@
         <v>665</v>
       </c>
       <c r="B57" t="s" s="6">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C57" t="s" s="6">
         <v>347</v>
@@ -20228,7 +20224,7 @@
         <v>631</v>
       </c>
       <c r="B58" t="s" s="6">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C58" t="s" s="6">
         <v>347</v>
@@ -20243,7 +20239,7 @@
         <v>667</v>
       </c>
       <c r="B59" t="s" s="6">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C59" t="s" s="6">
         <v>347</v>
@@ -20255,10 +20251,10 @@
     </row>
     <row r="60" ht="13.65" customHeight="1">
       <c r="A60" t="s" s="6">
+        <v>838</v>
+      </c>
+      <c r="B60" t="s" s="6">
         <v>839</v>
-      </c>
-      <c r="B60" t="s" s="6">
-        <v>840</v>
       </c>
       <c r="C60" t="s" s="6">
         <v>347</v>
@@ -20270,10 +20266,10 @@
     </row>
     <row r="61" ht="13.65" customHeight="1">
       <c r="A61" t="s" s="6">
+        <v>840</v>
+      </c>
+      <c r="B61" t="s" s="3">
         <v>841</v>
-      </c>
-      <c r="B61" t="s" s="3">
-        <v>842</v>
       </c>
       <c r="C61" t="s" s="3">
         <v>347</v>
@@ -20285,10 +20281,10 @@
     </row>
     <row r="62" ht="13.65" customHeight="1">
       <c r="A62" t="s" s="6">
+        <v>842</v>
+      </c>
+      <c r="B62" t="s" s="6">
         <v>843</v>
-      </c>
-      <c r="B62" t="s" s="6">
-        <v>844</v>
       </c>
       <c r="C62" t="s" s="6">
         <v>347</v>
@@ -20303,7 +20299,7 @@
         <v>711</v>
       </c>
       <c r="B63" t="s" s="3">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C63" t="s" s="3">
         <v>347</v>
@@ -20318,7 +20314,7 @@
         <v>696</v>
       </c>
       <c r="B64" t="s" s="3">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C64" t="s" s="3">
         <v>347</v>
@@ -20330,10 +20326,10 @@
     </row>
     <row r="65" ht="13.65" customHeight="1">
       <c r="A65" t="s" s="3">
+        <v>846</v>
+      </c>
+      <c r="B65" t="s" s="3">
         <v>847</v>
-      </c>
-      <c r="B65" t="s" s="3">
-        <v>848</v>
       </c>
       <c r="C65" t="s" s="3">
         <v>347</v>
@@ -20348,7 +20344,7 @@
         <v>696</v>
       </c>
       <c r="B66" t="s" s="7">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C66" t="s" s="7">
         <v>347</v>
@@ -20363,7 +20359,7 @@
         <v>711</v>
       </c>
       <c r="B67" t="s" s="7">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C67" t="s" s="7">
         <v>347</v>
@@ -20375,13 +20371,13 @@
     </row>
     <row r="68" ht="13.65" customHeight="1">
       <c r="A68" t="s" s="3">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B68" t="s" s="3">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C68" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D68" t="s" s="3">
         <v>767</v>
@@ -20390,13 +20386,13 @@
     </row>
     <row r="69" ht="13.65" customHeight="1">
       <c r="A69" t="s" s="6">
+        <v>851</v>
+      </c>
+      <c r="B69" t="s" s="6">
         <v>852</v>
       </c>
-      <c r="B69" t="s" s="6">
+      <c r="C69" t="s" s="6">
         <v>853</v>
-      </c>
-      <c r="C69" t="s" s="6">
-        <v>854</v>
       </c>
       <c r="D69" t="s" s="6">
         <v>767</v>
@@ -20405,13 +20401,13 @@
     </row>
     <row r="70" ht="13.65" customHeight="1">
       <c r="A70" t="s" s="3">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B70" t="s" s="3">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C70" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D70" t="s" s="3">
         <v>767</v>
@@ -20420,13 +20416,13 @@
     </row>
     <row r="71" ht="13.65" customHeight="1">
       <c r="A71" t="s" s="3">
+        <v>855</v>
+      </c>
+      <c r="B71" t="s" s="3">
         <v>856</v>
       </c>
-      <c r="B71" t="s" s="3">
-        <v>857</v>
-      </c>
       <c r="C71" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D71" t="s" s="3">
         <v>767</v>
@@ -20435,13 +20431,13 @@
     </row>
     <row r="72" ht="13.65" customHeight="1">
       <c r="A72" t="s" s="3">
+        <v>857</v>
+      </c>
+      <c r="B72" t="s" s="3">
         <v>858</v>
       </c>
-      <c r="B72" t="s" s="3">
-        <v>859</v>
-      </c>
       <c r="C72" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D72" t="s" s="3">
         <v>767</v>
@@ -20450,13 +20446,13 @@
     </row>
     <row r="73" ht="13.65" customHeight="1">
       <c r="A73" t="s" s="3">
+        <v>859</v>
+      </c>
+      <c r="B73" t="s" s="3">
         <v>860</v>
       </c>
-      <c r="B73" t="s" s="3">
-        <v>861</v>
-      </c>
       <c r="C73" t="s" s="3">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D73" t="s" s="3">
         <v>767</v>
@@ -20468,7 +20464,7 @@
         <v>738</v>
       </c>
       <c r="B74" t="s" s="3">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C74" t="s" s="3">
         <v>739</v>
@@ -20480,10 +20476,10 @@
     </row>
     <row r="75" ht="13.65" customHeight="1">
       <c r="A75" t="s" s="3">
+        <v>862</v>
+      </c>
+      <c r="B75" t="s" s="3">
         <v>863</v>
-      </c>
-      <c r="B75" t="s" s="3">
-        <v>864</v>
       </c>
       <c r="C75" t="s" s="3">
         <v>739</v>
@@ -20495,10 +20491,10 @@
     </row>
     <row r="76" ht="13.65" customHeight="1">
       <c r="A76" t="s" s="3">
+        <v>864</v>
+      </c>
+      <c r="B76" t="s" s="3">
         <v>865</v>
-      </c>
-      <c r="B76" t="s" s="3">
-        <v>866</v>
       </c>
       <c r="C76" t="s" s="3">
         <v>739</v>
@@ -20513,7 +20509,7 @@
         <v>738</v>
       </c>
       <c r="B77" t="s" s="7">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C77" t="s" s="7">
         <v>739</v>
@@ -20528,7 +20524,7 @@
         <v>618</v>
       </c>
       <c r="B78" t="s" s="3">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C78" t="s" s="3">
         <v>444</v>
@@ -20543,7 +20539,7 @@
         <v>753</v>
       </c>
       <c r="B79" t="s" s="8">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C79" t="s" s="8">
         <v>444</v>
@@ -20558,7 +20554,7 @@
         <v>443</v>
       </c>
       <c r="B80" t="s" s="3">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C80" t="s" s="3">
         <v>444</v>
@@ -20570,10 +20566,10 @@
     </row>
     <row r="81" ht="13.65" customHeight="1">
       <c r="A81" t="s" s="3">
+        <v>869</v>
+      </c>
+      <c r="B81" t="s" s="3">
         <v>870</v>
-      </c>
-      <c r="B81" t="s" s="3">
-        <v>871</v>
       </c>
       <c r="C81" t="s" s="3">
         <v>444</v>
@@ -20585,10 +20581,10 @@
     </row>
     <row r="82" ht="13.65" customHeight="1">
       <c r="A82" t="s" s="3">
+        <v>871</v>
+      </c>
+      <c r="B82" t="s" s="3">
         <v>872</v>
-      </c>
-      <c r="B82" t="s" s="3">
-        <v>873</v>
       </c>
       <c r="C82" t="s" s="3">
         <v>444</v>
@@ -20603,7 +20599,7 @@
         <v>627</v>
       </c>
       <c r="B83" t="s" s="6">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C83" t="s" s="6">
         <v>444</v>
@@ -20618,7 +20614,7 @@
         <v>747</v>
       </c>
       <c r="B84" t="s" s="3">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C84" t="s" s="3">
         <v>444</v>
@@ -20630,10 +20626,10 @@
     </row>
     <row r="85" ht="13.65" customHeight="1">
       <c r="A85" t="s" s="3">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B85" t="s" s="3">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C85" t="s" s="3">
         <v>444</v>
@@ -20645,10 +20641,10 @@
     </row>
     <row r="86" ht="13.65" customHeight="1">
       <c r="A86" t="s" s="3">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B86" t="s" s="3">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C86" t="s" s="3">
         <v>444</v>
@@ -20660,10 +20656,10 @@
     </row>
     <row r="87" ht="13.65" customHeight="1">
       <c r="A87" t="s" s="3">
+        <v>877</v>
+      </c>
+      <c r="B87" t="s" s="3">
         <v>878</v>
-      </c>
-      <c r="B87" t="s" s="3">
-        <v>879</v>
       </c>
       <c r="C87" t="s" s="3">
         <v>444</v>
@@ -20675,10 +20671,10 @@
     </row>
     <row r="88" ht="13.65" customHeight="1">
       <c r="A88" t="s" s="3">
+        <v>879</v>
+      </c>
+      <c r="B88" t="s" s="3">
         <v>880</v>
-      </c>
-      <c r="B88" t="s" s="3">
-        <v>881</v>
       </c>
       <c r="C88" t="s" s="3">
         <v>444</v>
@@ -20690,10 +20686,10 @@
     </row>
     <row r="89" ht="13.65" customHeight="1">
       <c r="A89" t="s" s="3">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B89" t="s" s="3">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C89" t="s" s="3">
         <v>444</v>
@@ -20705,10 +20701,10 @@
     </row>
     <row r="90" ht="13.65" customHeight="1">
       <c r="A90" t="s" s="3">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B90" t="s" s="3">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C90" t="s" s="3">
         <v>444</v>
@@ -20720,10 +20716,10 @@
     </row>
     <row r="91" ht="13.65" customHeight="1">
       <c r="A91" t="s" s="3">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B91" t="s" s="3">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C91" t="s" s="3">
         <v>444</v>
@@ -20735,10 +20731,10 @@
     </row>
     <row r="92" ht="13.65" customHeight="1">
       <c r="A92" t="s" s="3">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B92" t="s" s="3">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C92" t="s" s="3">
         <v>444</v>
@@ -20750,10 +20746,10 @@
     </row>
     <row r="93" ht="13.65" customHeight="1">
       <c r="A93" t="s" s="3">
+        <v>885</v>
+      </c>
+      <c r="B93" t="s" s="3">
         <v>886</v>
-      </c>
-      <c r="B93" t="s" s="3">
-        <v>887</v>
       </c>
       <c r="C93" t="s" s="3">
         <v>444</v>
@@ -20768,7 +20764,7 @@
         <v>629</v>
       </c>
       <c r="B94" t="s" s="6">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C94" t="s" s="6">
         <v>444</v>
@@ -20783,7 +20779,7 @@
         <v>663</v>
       </c>
       <c r="B95" t="s" s="6">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C95" t="s" s="6">
         <v>444</v>
@@ -20798,7 +20794,7 @@
         <v>737</v>
       </c>
       <c r="B96" t="s" s="3">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C96" t="s" s="3">
         <v>444</v>
@@ -20810,10 +20806,10 @@
     </row>
     <row r="97" ht="13.65" customHeight="1">
       <c r="A97" t="s" s="3">
+        <v>890</v>
+      </c>
+      <c r="B97" t="s" s="3">
         <v>891</v>
-      </c>
-      <c r="B97" t="s" s="3">
-        <v>892</v>
       </c>
       <c r="C97" t="s" s="3">
         <v>444</v>
@@ -20825,10 +20821,10 @@
     </row>
     <row r="98" ht="13.65" customHeight="1">
       <c r="A98" t="s" s="3">
+        <v>892</v>
+      </c>
+      <c r="B98" t="s" s="3">
         <v>893</v>
-      </c>
-      <c r="B98" t="s" s="3">
-        <v>894</v>
       </c>
       <c r="C98" t="s" s="3">
         <v>444</v>
@@ -20843,7 +20839,7 @@
         <v>729</v>
       </c>
       <c r="B99" t="s" s="3">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C99" t="s" s="3">
         <v>444</v>
@@ -20858,7 +20854,7 @@
         <v>747</v>
       </c>
       <c r="B100" t="s" s="7">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C100" t="s" s="7">
         <v>444</v>
@@ -20870,10 +20866,10 @@
     </row>
     <row r="101" ht="13.65" customHeight="1">
       <c r="A101" t="s" s="3">
+        <v>896</v>
+      </c>
+      <c r="B101" t="s" s="3">
         <v>897</v>
-      </c>
-      <c r="B101" t="s" s="3">
-        <v>898</v>
       </c>
       <c r="C101" t="s" s="3">
         <v>444</v>
@@ -20885,10 +20881,10 @@
     </row>
     <row r="102" ht="13.65" customHeight="1">
       <c r="A102" t="s" s="3">
+        <v>898</v>
+      </c>
+      <c r="B102" t="s" s="3">
         <v>899</v>
-      </c>
-      <c r="B102" t="s" s="3">
-        <v>900</v>
       </c>
       <c r="C102" t="s" s="3">
         <v>444</v>
@@ -20900,10 +20896,10 @@
     </row>
     <row r="103" ht="13.65" customHeight="1">
       <c r="A103" t="s" s="3">
+        <v>900</v>
+      </c>
+      <c r="B103" t="s" s="3">
         <v>901</v>
-      </c>
-      <c r="B103" t="s" s="3">
-        <v>902</v>
       </c>
       <c r="C103" t="s" s="3">
         <v>444</v>
@@ -20915,10 +20911,10 @@
     </row>
     <row r="104" ht="13.65" customHeight="1">
       <c r="A104" t="s" s="3">
+        <v>902</v>
+      </c>
+      <c r="B104" t="s" s="3">
         <v>903</v>
-      </c>
-      <c r="B104" t="s" s="3">
-        <v>904</v>
       </c>
       <c r="C104" t="s" s="3">
         <v>444</v>
@@ -20930,10 +20926,10 @@
     </row>
     <row r="105" ht="13.65" customHeight="1">
       <c r="A105" t="s" s="3">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B105" t="s" s="3">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C105" t="s" s="3">
         <v>444</v>
@@ -20948,7 +20944,7 @@
         <v>730</v>
       </c>
       <c r="B106" t="s" s="3">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C106" t="s" s="3">
         <v>444</v>
@@ -20960,10 +20956,10 @@
     </row>
     <row r="107" ht="13.65" customHeight="1">
       <c r="A107" t="s" s="7">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B107" t="s" s="7">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C107" t="s" s="7">
         <v>444</v>
@@ -20975,10 +20971,10 @@
     </row>
     <row r="108" ht="13.65" customHeight="1">
       <c r="A108" t="s" s="3">
+        <v>907</v>
+      </c>
+      <c r="B108" t="s" s="3">
         <v>908</v>
-      </c>
-      <c r="B108" t="s" s="3">
-        <v>909</v>
       </c>
       <c r="C108" t="s" s="3">
         <v>7</v>
@@ -20990,10 +20986,10 @@
     </row>
     <row r="109" ht="13.65" customHeight="1">
       <c r="A109" t="s" s="6">
+        <v>909</v>
+      </c>
+      <c r="B109" t="s" s="3">
         <v>910</v>
-      </c>
-      <c r="B109" t="s" s="3">
-        <v>911</v>
       </c>
       <c r="C109" t="s" s="3">
         <v>7</v>
@@ -21005,10 +21001,10 @@
     </row>
     <row r="110" ht="13.65" customHeight="1">
       <c r="A110" t="s" s="7">
+        <v>911</v>
+      </c>
+      <c r="B110" t="s" s="7">
         <v>912</v>
-      </c>
-      <c r="B110" t="s" s="7">
-        <v>913</v>
       </c>
       <c r="C110" t="s" s="7">
         <v>7</v>
@@ -21020,10 +21016,10 @@
     </row>
     <row r="111" ht="13.65" customHeight="1">
       <c r="A111" t="s" s="3">
+        <v>913</v>
+      </c>
+      <c r="B111" t="s" s="3">
         <v>914</v>
-      </c>
-      <c r="B111" t="s" s="3">
-        <v>915</v>
       </c>
       <c r="C111" t="s" s="3">
         <v>7</v>
@@ -21035,10 +21031,10 @@
     </row>
     <row r="112" ht="13.65" customHeight="1">
       <c r="A112" t="s" s="3">
+        <v>915</v>
+      </c>
+      <c r="B112" t="s" s="3">
         <v>916</v>
-      </c>
-      <c r="B112" t="s" s="3">
-        <v>917</v>
       </c>
       <c r="C112" t="s" s="3">
         <v>7</v>
@@ -21050,10 +21046,10 @@
     </row>
     <row r="113" ht="13.65" customHeight="1">
       <c r="A113" t="s" s="3">
+        <v>917</v>
+      </c>
+      <c r="B113" t="s" s="3">
         <v>918</v>
-      </c>
-      <c r="B113" t="s" s="3">
-        <v>919</v>
       </c>
       <c r="C113" t="s" s="3">
         <v>7</v>
@@ -21065,10 +21061,10 @@
     </row>
     <row r="114" ht="13.65" customHeight="1">
       <c r="A114" t="s" s="7">
+        <v>907</v>
+      </c>
+      <c r="B114" t="s" s="7">
         <v>908</v>
-      </c>
-      <c r="B114" t="s" s="7">
-        <v>909</v>
       </c>
       <c r="C114" t="s" s="7">
         <v>7</v>
@@ -21080,10 +21076,10 @@
     </row>
     <row r="115" ht="13.65" customHeight="1">
       <c r="A115" t="s" s="3">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B115" t="s" s="3">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C115" t="s" s="3">
         <v>7</v>
@@ -21095,10 +21091,10 @@
     </row>
     <row r="116" ht="13.65" customHeight="1">
       <c r="A116" t="s" s="3">
+        <v>920</v>
+      </c>
+      <c r="B116" t="s" s="3">
         <v>921</v>
-      </c>
-      <c r="B116" t="s" s="3">
-        <v>922</v>
       </c>
       <c r="C116" t="s" s="3">
         <v>7</v>
@@ -21110,10 +21106,10 @@
     </row>
     <row r="117" ht="13.65" customHeight="1">
       <c r="A117" t="s" s="3">
+        <v>922</v>
+      </c>
+      <c r="B117" t="s" s="3">
         <v>923</v>
-      </c>
-      <c r="B117" t="s" s="3">
-        <v>924</v>
       </c>
       <c r="C117" t="s" s="3">
         <v>7</v>
@@ -21128,7 +21124,7 @@
         <v>746</v>
       </c>
       <c r="B118" t="s" s="6">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C118" t="s" s="6">
         <v>7</v>
@@ -21140,10 +21136,10 @@
     </row>
     <row r="119" ht="13.65" customHeight="1">
       <c r="A119" t="s" s="7">
+        <v>925</v>
+      </c>
+      <c r="B119" t="s" s="7">
         <v>926</v>
-      </c>
-      <c r="B119" t="s" s="7">
-        <v>927</v>
       </c>
       <c r="C119" t="s" s="7">
         <v>7</v>
@@ -21158,7 +21154,7 @@
         <v>701</v>
       </c>
       <c r="B120" t="s" s="3">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C120" t="s" s="3">
         <v>7</v>
@@ -21173,7 +21169,7 @@
         <v>703</v>
       </c>
       <c r="B121" t="s" s="3">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C121" t="s" s="3">
         <v>7</v>
@@ -21182,6 +21178,21 @@
         <v>767</v>
       </c>
       <c r="E121" s="4"/>
+    </row>
+    <row r="122" ht="13.65" customHeight="1">
+      <c r="A122" t="s" s="3">
+        <v>446</v>
+      </c>
+      <c r="B122" t="s" s="3">
+        <v>929</v>
+      </c>
+      <c r="C122" t="s" s="3">
+        <v>447</v>
+      </c>
+      <c r="D122" t="s" s="3">
+        <v>767</v>
+      </c>
+      <c r="E122" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
@@ -21197,7 +21208,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="5" width="12.6719" style="9" customWidth="1"/>
@@ -22103,23 +22114,23 @@
     </row>
     <row r="70" ht="13.65" customHeight="1">
       <c r="A70" t="s" s="3">
+        <v>168</v>
+      </c>
+      <c r="B70" t="s" s="3">
         <v>1081</v>
       </c>
-      <c r="B70" t="s" s="3">
-        <v>946</v>
-      </c>
       <c r="C70" t="s" s="3">
-        <v>946</v>
+        <v>1082</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="13"/>
     </row>
     <row r="71" ht="13.65" customHeight="1">
       <c r="A71" t="s" s="3">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B71" t="s" s="3">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C71" t="s" s="3">
         <v>1084</v>
@@ -22155,10 +22166,10 @@
     </row>
     <row r="74" ht="13.65" customHeight="1">
       <c r="A74" t="s" s="3">
+        <v>195</v>
+      </c>
+      <c r="B74" t="s" s="3">
         <v>1089</v>
-      </c>
-      <c r="B74" t="s" s="3">
-        <v>1090</v>
       </c>
       <c r="C74" t="s" s="3">
         <v>1090</v>
@@ -22168,36 +22179,36 @@
     </row>
     <row r="75" ht="13.65" customHeight="1">
       <c r="A75" t="s" s="3">
-        <v>195</v>
+        <v>1091</v>
       </c>
       <c r="B75" t="s" s="3">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C75" t="s" s="3">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D75" s="12"/>
       <c r="E75" s="13"/>
     </row>
     <row r="76" ht="13.65" customHeight="1">
       <c r="A76" t="s" s="3">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B76" t="s" s="3">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C76" t="s" s="3">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D76" s="12"/>
       <c r="E76" s="13"/>
     </row>
     <row r="77" ht="13.65" customHeight="1">
       <c r="A77" t="s" s="3">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B77" t="s" s="3">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C77" t="s" s="3">
         <v>1098</v>
@@ -22207,20 +22218,20 @@
     </row>
     <row r="78" ht="13.65" customHeight="1">
       <c r="A78" t="s" s="3">
+        <v>238</v>
+      </c>
+      <c r="B78" t="s" s="3">
         <v>1099</v>
       </c>
-      <c r="B78" t="s" s="3">
-        <v>1100</v>
-      </c>
       <c r="C78" t="s" s="3">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D78" s="12"/>
       <c r="E78" s="13"/>
     </row>
     <row r="79" ht="13.65" customHeight="1">
       <c r="A79" t="s" s="3">
-        <v>238</v>
+        <v>1100</v>
       </c>
       <c r="B79" t="s" s="3">
         <v>1101</v>
@@ -22239,173 +22250,173 @@
         <v>1103</v>
       </c>
       <c r="C80" t="s" s="3">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D80" s="12"/>
       <c r="E80" s="13"/>
     </row>
     <row r="81" ht="13.65" customHeight="1">
       <c r="A81" t="s" s="3">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B81" t="s" s="3">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C81" t="s" s="3">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D81" s="12"/>
       <c r="E81" s="13"/>
     </row>
     <row r="82" ht="13.65" customHeight="1">
       <c r="A82" t="s" s="3">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B82" t="s" s="3">
-        <v>1108</v>
+        <v>942</v>
       </c>
       <c r="C82" t="s" s="3">
-        <v>1109</v>
+        <v>943</v>
       </c>
       <c r="D82" s="12"/>
       <c r="E82" s="13"/>
     </row>
     <row r="83" ht="13.65" customHeight="1">
       <c r="A83" t="s" s="3">
+        <v>1109</v>
+      </c>
+      <c r="B83" t="s" s="3">
         <v>1110</v>
       </c>
-      <c r="B83" t="s" s="3">
-        <v>942</v>
-      </c>
       <c r="C83" t="s" s="3">
-        <v>943</v>
+        <v>1111</v>
       </c>
       <c r="D83" s="12"/>
       <c r="E83" s="13"/>
     </row>
     <row r="84" ht="13.65" customHeight="1">
-      <c r="A84" t="s" s="3">
-        <v>1111</v>
-      </c>
-      <c r="B84" t="s" s="3">
+      <c r="A84" t="s" s="6">
         <v>1112</v>
       </c>
-      <c r="C84" t="s" s="3">
+      <c r="B84" t="s" s="6">
         <v>1113</v>
+      </c>
+      <c r="C84" t="s" s="6">
+        <v>1114</v>
       </c>
       <c r="D84" s="12"/>
       <c r="E84" s="13"/>
     </row>
     <row r="85" ht="13.65" customHeight="1">
       <c r="A85" t="s" s="6">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B85" t="s" s="6">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C85" t="s" s="6">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D85" s="12"/>
       <c r="E85" s="13"/>
     </row>
     <row r="86" ht="13.65" customHeight="1">
       <c r="A86" t="s" s="6">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B86" t="s" s="6">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C86" t="s" s="6">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D86" s="12"/>
       <c r="E86" s="13"/>
     </row>
     <row r="87" ht="13.65" customHeight="1">
       <c r="A87" t="s" s="6">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B87" t="s" s="6">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C87" t="s" s="6">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="13"/>
     </row>
     <row r="88" ht="13.65" customHeight="1">
       <c r="A88" t="s" s="6">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B88" t="s" s="6">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C88" t="s" s="6">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D88" s="12"/>
       <c r="E88" s="13"/>
     </row>
     <row r="89" ht="13.65" customHeight="1">
       <c r="A89" t="s" s="6">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B89" t="s" s="6">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C89" t="s" s="6">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D89" s="12"/>
       <c r="E89" s="13"/>
     </row>
     <row r="90" ht="13.65" customHeight="1">
       <c r="A90" t="s" s="6">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B90" t="s" s="6">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C90" t="s" s="6">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D90" s="12"/>
       <c r="E90" s="13"/>
     </row>
     <row r="91" ht="13.65" customHeight="1">
       <c r="A91" t="s" s="6">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B91" t="s" s="6">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C91" t="s" s="6">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="13"/>
     </row>
     <row r="92" ht="13.65" customHeight="1">
       <c r="A92" t="s" s="6">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B92" t="s" s="6">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C92" t="s" s="6">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D92" s="12"/>
       <c r="E92" s="13"/>
     </row>
     <row r="93" ht="13.65" customHeight="1">
       <c r="A93" t="s" s="6">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B93" t="s" s="6">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C93" t="s" s="6">
         <v>1140</v>
@@ -22421,17 +22432,17 @@
         <v>1142</v>
       </c>
       <c r="C94" t="s" s="6">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D94" s="12"/>
       <c r="E94" s="13"/>
     </row>
     <row r="95" ht="13.65" customHeight="1">
       <c r="A95" t="s" s="6">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B95" t="s" s="6">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C95" t="s" s="6">
         <v>1145</v>
@@ -22447,43 +22458,43 @@
         <v>1147</v>
       </c>
       <c r="C96" t="s" s="6">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="13"/>
     </row>
     <row r="97" ht="13.65" customHeight="1">
       <c r="A97" t="s" s="6">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B97" t="s" s="6">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C97" t="s" s="6">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D97" s="12"/>
       <c r="E97" s="13"/>
     </row>
     <row r="98" ht="13.65" customHeight="1">
       <c r="A98" t="s" s="6">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B98" t="s" s="6">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C98" t="s" s="6">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D98" s="12"/>
       <c r="E98" s="13"/>
     </row>
     <row r="99" ht="13.65" customHeight="1">
       <c r="A99" t="s" s="6">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B99" t="s" s="6">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C99" t="s" s="6">
         <v>1156</v>
@@ -22499,69 +22510,69 @@
         <v>1158</v>
       </c>
       <c r="C100" t="s" s="6">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="13"/>
     </row>
     <row r="101" ht="13.65" customHeight="1">
       <c r="A101" t="s" s="6">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B101" t="s" s="6">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C101" t="s" s="6">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="13"/>
     </row>
     <row r="102" ht="13.65" customHeight="1">
       <c r="A102" t="s" s="6">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B102" t="s" s="6">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C102" t="s" s="6">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D102" s="12"/>
       <c r="E102" s="13"/>
     </row>
     <row r="103" ht="13.65" customHeight="1">
       <c r="A103" t="s" s="6">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B103" t="s" s="6">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C103" t="s" s="6">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D103" s="12"/>
       <c r="E103" s="13"/>
     </row>
     <row r="104" ht="13.65" customHeight="1">
       <c r="A104" t="s" s="6">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B104" t="s" s="6">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C104" t="s" s="6">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D104" s="12"/>
       <c r="E104" s="13"/>
     </row>
     <row r="105" ht="13.65" customHeight="1">
       <c r="A105" t="s" s="6">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B105" t="s" s="6">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C105" t="s" s="6">
         <v>1173</v>
@@ -22577,30 +22588,30 @@
         <v>1175</v>
       </c>
       <c r="C106" t="s" s="6">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D106" s="12"/>
       <c r="E106" s="13"/>
     </row>
     <row r="107" ht="13.65" customHeight="1">
       <c r="A107" t="s" s="6">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B107" t="s" s="6">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C107" t="s" s="6">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D107" s="12"/>
       <c r="E107" s="13"/>
     </row>
     <row r="108" ht="13.65" customHeight="1">
       <c r="A108" t="s" s="6">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B108" t="s" s="6">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C108" t="s" s="6">
         <v>1181</v>
@@ -22642,17 +22653,17 @@
         <v>1187</v>
       </c>
       <c r="C111" t="s" s="6">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D111" s="12"/>
       <c r="E111" s="13"/>
     </row>
     <row r="112" ht="13.65" customHeight="1">
       <c r="A112" t="s" s="6">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B112" t="s" s="6">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C112" t="s" s="6">
         <v>1190</v>
@@ -22668,17 +22679,17 @@
         <v>1192</v>
       </c>
       <c r="C113" t="s" s="6">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D113" s="12"/>
       <c r="E113" s="13"/>
     </row>
     <row r="114" ht="13.65" customHeight="1">
       <c r="A114" t="s" s="6">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B114" t="s" s="6">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C114" t="s" s="6">
         <v>1195</v>
@@ -22720,17 +22731,17 @@
         <v>1201</v>
       </c>
       <c r="C117" t="s" s="6">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D117" s="12"/>
       <c r="E117" s="13"/>
     </row>
     <row r="118" ht="13.65" customHeight="1">
       <c r="A118" t="s" s="6">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B118" t="s" s="6">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C118" t="s" s="6">
         <v>1204</v>
@@ -22753,114 +22764,114 @@
     </row>
     <row r="120" ht="13.65" customHeight="1">
       <c r="A120" t="s" s="6">
-        <v>1207</v>
+        <v>205</v>
       </c>
       <c r="B120" t="s" s="6">
-        <v>1208</v>
+        <v>1016</v>
       </c>
       <c r="C120" t="s" s="6">
-        <v>1208</v>
+        <v>1016</v>
       </c>
       <c r="D120" s="12"/>
       <c r="E120" s="13"/>
     </row>
     <row r="121" ht="13.65" customHeight="1">
       <c r="A121" t="s" s="6">
-        <v>205</v>
+        <v>1207</v>
       </c>
       <c r="B121" t="s" s="6">
-        <v>1016</v>
+        <v>1208</v>
       </c>
       <c r="C121" t="s" s="6">
-        <v>1016</v>
+        <v>1209</v>
       </c>
       <c r="D121" s="12"/>
       <c r="E121" s="13"/>
     </row>
     <row r="122" ht="13.65" customHeight="1">
       <c r="A122" t="s" s="6">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B122" t="s" s="6">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C122" t="s" s="6">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D122" s="12"/>
       <c r="E122" s="13"/>
     </row>
     <row r="123" ht="13.65" customHeight="1">
       <c r="A123" t="s" s="6">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B123" t="s" s="6">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C123" t="s" s="6">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D123" s="12"/>
       <c r="E123" s="13"/>
     </row>
     <row r="124" ht="13.65" customHeight="1">
       <c r="A124" t="s" s="6">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B124" t="s" s="6">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="C124" t="s" s="6">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D124" s="12"/>
       <c r="E124" s="13"/>
     </row>
     <row r="125" ht="13.65" customHeight="1">
       <c r="A125" t="s" s="6">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B125" t="s" s="6">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C125" t="s" s="6">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D125" s="12"/>
       <c r="E125" s="13"/>
     </row>
     <row r="126" ht="13.65" customHeight="1">
       <c r="A126" t="s" s="6">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B126" t="s" s="6">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C126" t="s" s="6">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D126" s="12"/>
       <c r="E126" s="13"/>
     </row>
     <row r="127" ht="13.65" customHeight="1">
       <c r="A127" t="s" s="6">
-        <v>1224</v>
-      </c>
-      <c r="B127" t="s" s="6">
         <v>1225</v>
       </c>
+      <c r="B127" t="s" s="14">
+        <v>1226</v>
+      </c>
       <c r="C127" t="s" s="6">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D127" s="12"/>
       <c r="E127" s="13"/>
     </row>
     <row r="128" ht="13.65" customHeight="1">
       <c r="A128" t="s" s="6">
-        <v>1227</v>
-      </c>
-      <c r="B128" t="s" s="14">
         <v>1228</v>
+      </c>
+      <c r="B128" t="s" s="6">
+        <v>1229</v>
       </c>
       <c r="C128" t="s" s="6">
         <v>1229</v>
@@ -22870,120 +22881,81 @@
     </row>
     <row r="129" ht="13.65" customHeight="1">
       <c r="A129" t="s" s="6">
-        <v>17</v>
+        <v>1230</v>
       </c>
       <c r="B129" t="s" s="6">
-        <v>944</v>
+        <v>1231</v>
       </c>
       <c r="C129" t="s" s="6">
-        <v>945</v>
+        <v>1232</v>
       </c>
       <c r="D129" s="12"/>
       <c r="E129" s="13"/>
     </row>
     <row r="130" ht="13.65" customHeight="1">
       <c r="A130" t="s" s="6">
-        <v>1230</v>
+        <v>990</v>
       </c>
       <c r="B130" t="s" s="6">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C130" t="s" s="6">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D130" s="12"/>
       <c r="E130" s="13"/>
     </row>
     <row r="131" ht="13.65" customHeight="1">
       <c r="A131" t="s" s="6">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B131" t="s" s="6">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="C131" t="s" s="6">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="D131" s="12"/>
       <c r="E131" s="13"/>
     </row>
     <row r="132" ht="13.65" customHeight="1">
       <c r="A132" t="s" s="6">
-        <v>79</v>
+        <v>1236</v>
       </c>
       <c r="B132" t="s" s="6">
-        <v>984</v>
+        <v>1237</v>
       </c>
       <c r="C132" t="s" s="6">
-        <v>984</v>
+        <v>1237</v>
       </c>
       <c r="D132" s="12"/>
       <c r="E132" s="13"/>
     </row>
     <row r="133" ht="13.65" customHeight="1">
       <c r="A133" t="s" s="6">
-        <v>990</v>
+        <v>1238</v>
       </c>
       <c r="B133" t="s" s="6">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="C133" t="s" s="6">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="D133" s="12"/>
       <c r="E133" s="13"/>
     </row>
     <row r="134" ht="13.65" customHeight="1">
       <c r="A134" t="s" s="6">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="B134" t="s" s="6">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="C134" t="s" s="6">
-        <v>1237</v>
-      </c>
-      <c r="D134" s="12"/>
-      <c r="E134" s="13"/>
-    </row>
-    <row r="135" ht="13.65" customHeight="1">
-      <c r="A135" t="s" s="6">
-        <v>1238</v>
-      </c>
-      <c r="B135" t="s" s="6">
-        <v>1239</v>
-      </c>
-      <c r="C135" t="s" s="6">
-        <v>1239</v>
-      </c>
-      <c r="D135" s="12"/>
-      <c r="E135" s="13"/>
-    </row>
-    <row r="136" ht="13.65" customHeight="1">
-      <c r="A136" t="s" s="6">
-        <v>1240</v>
-      </c>
-      <c r="B136" t="s" s="6">
-        <v>1241</v>
-      </c>
-      <c r="C136" t="s" s="6">
-        <v>1242</v>
-      </c>
-      <c r="D136" s="12"/>
-      <c r="E136" s="13"/>
-    </row>
-    <row r="137" ht="13.65" customHeight="1">
-      <c r="A137" t="s" s="6">
         <v>1243</v>
       </c>
-      <c r="B137" t="s" s="6">
-        <v>1244</v>
-      </c>
-      <c r="C137" t="s" s="6">
-        <v>1245</v>
-      </c>
-      <c r="D137" s="15"/>
-      <c r="E137" s="16"/>
+      <c r="D134" s="15"/>
+      <c r="E134" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
